--- a/ontology/v2.01/cellfie_import.xlsx
+++ b/ontology/v2.01/cellfie_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riccasi/Documents/GitHub/bedreflyt/ontology/v2.01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDCF2B8-6747-DF4E-A4EE-504C20000CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CF28EE-1476-FC49-877C-2049B57FE7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25600" yWindow="-1360" windowWidth="25600" windowHeight="28300" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
+    <workbookView xWindow="-25600" yWindow="-1360" windowWidth="25600" windowHeight="28300" activeTab="7" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
   </bookViews>
   <sheets>
     <sheet name="TreatmentJourneys" sheetId="1" r:id="rId1"/>
@@ -468,10 +468,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/ontology/v2.01/cellfie_import.xlsx
+++ b/ontology/v2.01/cellfie_import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riccasi/Documents/GitHub/bedreflyt/ontology/v2.01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurasla/Documents/GitHub/bedreflyt/ontology/v2.01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CF28EE-1476-FC49-877C-2049B57FE7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A97D91-6CDA-054F-B3C3-276A6D25A74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25600" yWindow="-1360" windowWidth="25600" windowHeight="28300" activeTab="7" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
+    <workbookView xWindow="4440" yWindow="1220" windowWidth="44580" windowHeight="24560" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
   </bookViews>
   <sheets>
     <sheet name="TreatmentJourneys" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="121">
   <si>
     <t>DIAGNOSIS</t>
   </si>
@@ -401,13 +400,19 @@
   </si>
   <si>
     <t>LAST STEP</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>TotalStepNs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -425,6 +430,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -450,9 +462,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -787,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B973482-F93F-2340-91C4-4A18BF01CE10}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -799,7 +812,7 @@
     <col min="7" max="7" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,8 +834,11 @@
       <c r="G1" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -844,8 +860,11 @@
       <c r="G2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -867,8 +886,11 @@
       <c r="G3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -890,8 +912,11 @@
       <c r="G4" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -913,8 +938,11 @@
       <c r="G5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -936,8 +964,11 @@
       <c r="G6" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -959,8 +990,11 @@
       <c r="G7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -982,8 +1016,11 @@
       <c r="G8" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -1005,8 +1042,11 @@
       <c r="G9" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -1028,8 +1068,11 @@
       <c r="G10" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1051,8 +1094,11 @@
       <c r="G11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -1074,8 +1120,11 @@
       <c r="G12" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1096,6 +1145,9 @@
       </c>
       <c r="G13" t="s">
         <v>107</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1105,3498 +1157,3932 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{272AE597-DF5B-6144-9B2B-E3571D9F6B3C}">
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" customWidth="1"/>
-    <col min="2" max="4" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="5" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>94</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>77</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>53</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
         <v>78</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>79</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>53</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>79</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>80</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>78</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>89</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>53</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
         <v>80</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>81</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
       <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>4</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>53</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
         <v>81</v>
       </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
       <c r="D5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
       <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>90</v>
       </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" t="s">
-        <v>82</v>
+      <c r="B6">
+        <v>4</v>
       </c>
       <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
         <v>83</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
       <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>53</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
         <v>83</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>84</v>
       </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
+      <c r="E7" t="s">
+        <v>82</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>91</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>53</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
         <v>84</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>85</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>83</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>4</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>91</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
         <v>85</v>
       </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
       <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
         <v>84</v>
       </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
       <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
         <v>4</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>85</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>53</v>
       </c>
-      <c r="B10" t="s">
-        <v>82</v>
+      <c r="B10">
+        <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
         <v>86</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>85</v>
       </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
       <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
         <v>4</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>53</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
         <v>86</v>
       </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
       <c r="D11" t="s">
         <v>82</v>
       </c>
-      <c r="E11">
-        <v>0</v>
+      <c r="E11" t="s">
+        <v>82</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>4</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>92</v>
       </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>53</v>
       </c>
-      <c r="B12" t="s">
-        <v>82</v>
+      <c r="B12">
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
         <v>86</v>
       </c>
-      <c r="E12">
-        <v>3</v>
+      <c r="E12" t="s">
+        <v>86</v>
       </c>
       <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
         <v>4</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>53</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
         <v>86</v>
       </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
       <c r="D13" t="s">
         <v>82</v>
       </c>
-      <c r="E13">
-        <v>0</v>
+      <c r="E13" t="s">
+        <v>82</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>4</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>92</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>53</v>
       </c>
-      <c r="B14" t="s">
-        <v>82</v>
+      <c r="B14">
+        <v>12</v>
       </c>
       <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
         <v>87</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>86</v>
       </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
       <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
         <v>4</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>53</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
         <v>87</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>88</v>
       </c>
-      <c r="D15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
+      <c r="E15" t="s">
+        <v>82</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>4</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>93</v>
       </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>53</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
         <v>88</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>87</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
       <c r="F16">
-        <v>3</v>
-      </c>
-      <c r="G16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16" t="s">
         <v>93</v>
       </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>54</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
         <v>78</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>79</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
       <c r="F17">
         <v>0</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>54</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
         <v>79</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>80</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>78</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
       <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
         <v>4</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>89</v>
       </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>54</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
         <v>80</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>81</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>79</v>
       </c>
-      <c r="E19">
-        <v>3</v>
-      </c>
       <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19">
         <v>4</v>
       </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>54</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
         <v>81</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>95</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>80</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
       <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>4</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>90</v>
       </c>
-      <c r="H20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>54</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
         <v>95</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>85</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>81</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>4</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>90</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>54</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
         <v>85</v>
       </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
       <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s">
         <v>95</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <v>4</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>85</v>
       </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>54</v>
       </c>
-      <c r="B23" t="s">
-        <v>82</v>
+      <c r="B23">
+        <v>6</v>
       </c>
       <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
         <v>86</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>85</v>
       </c>
-      <c r="E23">
-        <v>3</v>
-      </c>
       <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
         <v>4</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>54</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
         <v>86</v>
       </c>
-      <c r="C24" t="s">
-        <v>82</v>
-      </c>
       <c r="D24" t="s">
         <v>82</v>
       </c>
-      <c r="E24">
-        <v>0</v>
+      <c r="E24" t="s">
+        <v>82</v>
       </c>
       <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
         <v>4</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>92</v>
       </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>54</v>
       </c>
-      <c r="B25" t="s">
-        <v>82</v>
+      <c r="B25">
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
         <v>86</v>
       </c>
-      <c r="E25">
-        <v>3</v>
+      <c r="E25" t="s">
+        <v>86</v>
       </c>
       <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
         <v>4</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>54</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
         <v>86</v>
       </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
       <c r="D26" t="s">
         <v>82</v>
       </c>
-      <c r="E26">
-        <v>0</v>
+      <c r="E26" t="s">
+        <v>82</v>
       </c>
       <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
         <v>4</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>92</v>
       </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>54</v>
       </c>
-      <c r="B27" t="s">
-        <v>82</v>
+      <c r="B27">
+        <v>10</v>
       </c>
       <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" t="s">
         <v>87</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>86</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <v>4</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>54</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
         <v>87</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>88</v>
       </c>
-      <c r="D28" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
+      <c r="E28" t="s">
+        <v>82</v>
       </c>
       <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
         <v>4</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>93</v>
       </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>54</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
         <v>88</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>87</v>
       </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
       <c r="F29">
-        <v>3</v>
-      </c>
-      <c r="G29" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
+      <c r="H29" t="s">
         <v>93</v>
       </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>55</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
         <v>78</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>96</v>
       </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
       <c r="F30">
         <v>0</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>55</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>96</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>80</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>78</v>
       </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
       <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
         <v>101</v>
       </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>55</v>
       </c>
-      <c r="B32" t="s">
-        <v>80</v>
+      <c r="B32">
+        <v>2</v>
       </c>
       <c r="C32" t="s">
         <v>80</v>
       </c>
       <c r="D32" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" t="s">
         <v>96</v>
       </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
       <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
         <v>102</v>
       </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>55</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
         <v>80</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>95</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>80</v>
       </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
       <c r="F33">
         <v>1</v>
       </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>55</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
         <v>95</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>97</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>80</v>
       </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
       <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
         <v>90</v>
       </c>
-      <c r="H34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>55</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
         <v>97</v>
       </c>
-      <c r="C35" t="s">
-        <v>82</v>
-      </c>
       <c r="D35" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" t="s">
         <v>95</v>
       </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
       <c r="F35">
-        <v>2</v>
-      </c>
-      <c r="G35" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35" t="s">
         <v>85</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>55</v>
       </c>
-      <c r="B36" t="s">
-        <v>82</v>
+      <c r="B36">
+        <v>6</v>
       </c>
       <c r="C36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" t="s">
         <v>98</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>97</v>
       </c>
-      <c r="E36">
-        <v>2</v>
-      </c>
       <c r="F36">
         <v>2</v>
       </c>
-      <c r="H36">
+      <c r="G36">
+        <v>2</v>
+      </c>
+      <c r="I36">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>55</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
         <v>98</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>99</v>
       </c>
-      <c r="D37" t="s">
-        <v>82</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
+      <c r="E37" t="s">
+        <v>82</v>
       </c>
       <c r="F37">
-        <v>2</v>
-      </c>
-      <c r="G37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37" t="s">
         <v>92</v>
       </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>55</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
         <v>99</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>100</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>98</v>
       </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
       <c r="F38">
         <v>1</v>
       </c>
-      <c r="H38">
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="I38">
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>55</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
         <v>100</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>99</v>
       </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
       <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
         <v>103</v>
       </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>56</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40" t="s">
         <v>78</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>104</v>
       </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
       <c r="F40">
         <v>0</v>
       </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>56</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
         <v>104</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>105</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>78</v>
       </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
       <c r="F41">
-        <v>2</v>
-      </c>
-      <c r="G41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+      <c r="H41" t="s">
         <v>108</v>
       </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>56</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
         <v>105</v>
       </c>
-      <c r="C42" t="s">
-        <v>82</v>
-      </c>
       <c r="D42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" t="s">
         <v>104</v>
       </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
       <c r="F42">
-        <v>2</v>
-      </c>
-      <c r="G42" t="s">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42" t="s">
         <v>109</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>56</v>
       </c>
-      <c r="B43" t="s">
-        <v>82</v>
+      <c r="B43">
+        <v>3</v>
       </c>
       <c r="C43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" t="s">
         <v>80</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>105</v>
       </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
       <c r="F43">
-        <v>2</v>
-      </c>
-      <c r="G43" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43" t="s">
         <v>99</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>56</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
         <v>80</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>106</v>
       </c>
-      <c r="D44" t="s">
-        <v>82</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
+      <c r="E44" t="s">
+        <v>82</v>
       </c>
       <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44" t="s">
         <v>110</v>
       </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>56</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45">
+        <v>5</v>
+      </c>
+      <c r="C45" t="s">
         <v>106</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>97</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>80</v>
       </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
       <c r="F45">
-        <v>2</v>
-      </c>
-      <c r="G45" t="s">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+      <c r="H45" t="s">
         <v>111</v>
       </c>
-      <c r="H45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>56</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
         <v>97</v>
       </c>
-      <c r="C46" t="s">
-        <v>82</v>
-      </c>
       <c r="D46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" t="s">
         <v>106</v>
       </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
       <c r="F46">
-        <v>3</v>
-      </c>
-      <c r="G46" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+      <c r="H46" t="s">
         <v>85</v>
       </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>56</v>
       </c>
-      <c r="B47" t="s">
-        <v>82</v>
+      <c r="B47">
+        <v>7</v>
       </c>
       <c r="C47" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" t="s">
         <v>86</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>97</v>
       </c>
-      <c r="E47">
-        <v>2</v>
-      </c>
       <c r="F47">
-        <v>3</v>
-      </c>
-      <c r="G47" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <v>3</v>
+      </c>
+      <c r="H47" t="s">
         <v>112</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>56</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
         <v>86</v>
       </c>
-      <c r="C48" t="s">
-        <v>82</v>
-      </c>
       <c r="D48" t="s">
         <v>82</v>
       </c>
-      <c r="E48">
-        <v>0</v>
+      <c r="E48" t="s">
+        <v>82</v>
       </c>
       <c r="F48">
-        <v>3</v>
-      </c>
-      <c r="G48" t="s">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="H48" t="s">
         <v>92</v>
       </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>56</v>
       </c>
-      <c r="B49" t="s">
-        <v>82</v>
+      <c r="B49">
+        <v>9</v>
       </c>
       <c r="C49" t="s">
         <v>82</v>
       </c>
       <c r="D49" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" t="s">
         <v>86</v>
       </c>
-      <c r="E49">
-        <v>2</v>
-      </c>
       <c r="F49">
-        <v>3</v>
-      </c>
-      <c r="G49" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49">
+        <v>3</v>
+      </c>
+      <c r="H49" t="s">
         <v>9</v>
       </c>
-      <c r="H49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>56</v>
       </c>
-      <c r="B50" t="s">
-        <v>82</v>
+      <c r="B50">
+        <v>10</v>
       </c>
       <c r="C50" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" t="s">
         <v>107</v>
       </c>
-      <c r="D50" t="s">
-        <v>82</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
+      <c r="E50" t="s">
+        <v>82</v>
       </c>
       <c r="F50">
-        <v>3</v>
-      </c>
-      <c r="G50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>3</v>
+      </c>
+      <c r="H50" t="s">
         <v>8</v>
       </c>
-      <c r="H50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>56</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
         <v>107</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>88</v>
       </c>
-      <c r="D51" t="s">
-        <v>82</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
+      <c r="E51" t="s">
+        <v>82</v>
       </c>
       <c r="F51">
-        <v>3</v>
-      </c>
-      <c r="G51" t="s">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>3</v>
+      </c>
+      <c r="H51" t="s">
         <v>113</v>
       </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>56</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52">
+        <v>12</v>
+      </c>
+      <c r="C52" t="s">
         <v>88</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>107</v>
       </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
       <c r="F52">
-        <v>3</v>
-      </c>
-      <c r="G52" t="s">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+      <c r="H52" t="s">
         <v>113</v>
       </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>57</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53" t="s">
         <v>78</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>79</v>
       </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
       <c r="F53">
         <v>0</v>
       </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>57</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
         <v>79</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>80</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>78</v>
       </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
       <c r="F54">
-        <v>2</v>
-      </c>
-      <c r="G54" t="s">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+      <c r="H54" t="s">
         <v>89</v>
       </c>
-      <c r="H54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>57</v>
       </c>
-      <c r="B55" t="s">
-        <v>80</v>
+      <c r="B55">
+        <v>2</v>
       </c>
       <c r="C55" t="s">
         <v>80</v>
       </c>
       <c r="D55" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" t="s">
         <v>79</v>
       </c>
-      <c r="E55">
-        <v>2</v>
-      </c>
       <c r="F55">
         <v>2</v>
       </c>
-      <c r="H55">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>57</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56">
+        <v>3</v>
+      </c>
+      <c r="C56" t="s">
         <v>80</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>95</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>80</v>
       </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
       <c r="F56">
-        <v>2</v>
-      </c>
-      <c r="H56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>57</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
         <v>95</v>
       </c>
-      <c r="C57" t="s">
-        <v>82</v>
-      </c>
       <c r="D57" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" t="s">
         <v>80</v>
       </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
       <c r="F57">
-        <v>3</v>
-      </c>
-      <c r="G57" t="s">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>3</v>
+      </c>
+      <c r="H57" t="s">
         <v>90</v>
       </c>
-      <c r="H57">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>82</v>
+      <c r="B58">
+        <v>5</v>
       </c>
       <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" t="s">
         <v>86</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>95</v>
       </c>
-      <c r="E58">
-        <v>2</v>
-      </c>
       <c r="F58">
-        <v>3</v>
-      </c>
-      <c r="H58">
+        <v>2</v>
+      </c>
+      <c r="G58">
+        <v>3</v>
+      </c>
+      <c r="I58">
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>57</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59">
+        <v>6</v>
+      </c>
+      <c r="C59" t="s">
         <v>86</v>
       </c>
-      <c r="C59" t="s">
-        <v>82</v>
-      </c>
       <c r="D59" t="s">
         <v>82</v>
       </c>
-      <c r="E59">
-        <v>0</v>
+      <c r="E59" t="s">
+        <v>82</v>
       </c>
       <c r="F59">
-        <v>3</v>
-      </c>
-      <c r="G59" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59" t="s">
         <v>92</v>
       </c>
-      <c r="H59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>57</v>
       </c>
-      <c r="B60" t="s">
-        <v>82</v>
+      <c r="B60">
+        <v>7</v>
       </c>
       <c r="C60" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" t="s">
         <v>107</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>86</v>
       </c>
-      <c r="E60">
-        <v>2</v>
-      </c>
       <c r="F60">
-        <v>3</v>
-      </c>
-      <c r="H60">
+        <v>2</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+      <c r="I60">
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>57</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
         <v>107</v>
       </c>
-      <c r="D61" t="s">
-        <v>82</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
+      <c r="E61" t="s">
+        <v>82</v>
       </c>
       <c r="F61">
-        <v>2</v>
-      </c>
-      <c r="G61" t="s">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+      <c r="H61" t="s">
         <v>113</v>
       </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>115</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62" t="s">
         <v>78</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>96</v>
       </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
       <c r="F62">
         <v>0</v>
       </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>115</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
         <v>96</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>80</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>78</v>
       </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
       <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63" t="s">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
         <v>101</v>
       </c>
-      <c r="H63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>115</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
         <v>80</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>95</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>96</v>
       </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
       <c r="F64">
-        <v>1</v>
-      </c>
-      <c r="G64" t="s">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
         <v>116</v>
       </c>
-      <c r="H64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>115</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
         <v>95</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>97</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>80</v>
       </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
       <c r="F65">
-        <v>1</v>
-      </c>
-      <c r="G65" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
         <v>90</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>115</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
         <v>97</v>
       </c>
-      <c r="C66" t="s">
-        <v>82</v>
-      </c>
       <c r="D66" t="s">
+        <v>82</v>
+      </c>
+      <c r="E66" t="s">
         <v>95</v>
       </c>
-      <c r="E66">
-        <v>0</v>
-      </c>
       <c r="F66">
-        <v>2</v>
-      </c>
-      <c r="G66" t="s">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66" t="s">
         <v>85</v>
       </c>
-      <c r="H66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>115</v>
       </c>
-      <c r="B67" t="s">
-        <v>82</v>
+      <c r="B67">
+        <v>5</v>
       </c>
       <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" t="s">
         <v>114</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>97</v>
       </c>
-      <c r="E67">
-        <v>2</v>
-      </c>
       <c r="F67">
         <v>2</v>
       </c>
-      <c r="H67">
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="I67">
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>115</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
         <v>114</v>
       </c>
-      <c r="C68" t="s">
-        <v>82</v>
-      </c>
       <c r="D68" t="s">
         <v>82</v>
       </c>
-      <c r="E68">
-        <v>0</v>
+      <c r="E68" t="s">
+        <v>82</v>
       </c>
       <c r="F68">
-        <v>2</v>
-      </c>
-      <c r="G68" t="s">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68" t="s">
         <v>92</v>
       </c>
-      <c r="H68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>115</v>
       </c>
-      <c r="B69" t="s">
-        <v>82</v>
+      <c r="B69">
+        <v>7</v>
       </c>
       <c r="C69" t="s">
         <v>82</v>
       </c>
       <c r="D69" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" t="s">
         <v>114</v>
       </c>
-      <c r="E69">
-        <v>2</v>
-      </c>
       <c r="F69">
         <v>2</v>
       </c>
-      <c r="H69">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G69">
+        <v>2</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>115</v>
       </c>
-      <c r="B70" t="s">
-        <v>82</v>
+      <c r="B70">
+        <v>8</v>
       </c>
       <c r="C70" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70" t="s">
         <v>107</v>
       </c>
-      <c r="D70" t="s">
-        <v>82</v>
-      </c>
-      <c r="E70">
-        <v>1</v>
+      <c r="E70" t="s">
+        <v>82</v>
       </c>
       <c r="F70">
-        <v>2</v>
-      </c>
-      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>2</v>
+      </c>
+      <c r="I70">
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>115</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71">
+        <v>9</v>
+      </c>
+      <c r="C71" t="s">
         <v>107</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>100</v>
       </c>
-      <c r="D71" t="s">
-        <v>82</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
+      <c r="E71" t="s">
+        <v>82</v>
       </c>
       <c r="F71">
-        <v>1</v>
-      </c>
-      <c r="G71" t="s">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
         <v>103</v>
       </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>115</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s">
         <v>100</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>107</v>
       </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
       <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
         <v>113</v>
       </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>59</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73" t="s">
         <v>78</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>104</v>
       </c>
-      <c r="E73">
-        <v>0</v>
-      </c>
       <c r="F73">
         <v>0</v>
       </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>59</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
         <v>104</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>105</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>78</v>
       </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
       <c r="F74">
-        <v>1</v>
-      </c>
-      <c r="G74" t="s">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
         <v>101</v>
       </c>
-      <c r="H74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>59</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75" t="s">
         <v>105</v>
       </c>
-      <c r="C75" t="s">
-        <v>82</v>
-      </c>
       <c r="D75" t="s">
+        <v>82</v>
+      </c>
+      <c r="E75" t="s">
         <v>104</v>
       </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
       <c r="F75">
-        <v>1</v>
-      </c>
-      <c r="G75" t="s">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
         <v>109</v>
       </c>
-      <c r="H75">
+      <c r="I75">
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>59</v>
       </c>
-      <c r="B76" t="s">
-        <v>82</v>
+      <c r="B76">
+        <v>3</v>
       </c>
       <c r="C76" t="s">
+        <v>82</v>
+      </c>
+      <c r="D76" t="s">
         <v>80</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>105</v>
       </c>
-      <c r="E76">
-        <v>1</v>
-      </c>
       <c r="F76">
         <v>1</v>
       </c>
-      <c r="H76">
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="I76">
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>59</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
         <v>80</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>106</v>
       </c>
-      <c r="D77" t="s">
-        <v>82</v>
-      </c>
-      <c r="E77">
-        <v>1</v>
+      <c r="E77" t="s">
+        <v>82</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
-      <c r="H77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>59</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78">
+        <v>5</v>
+      </c>
+      <c r="C78" t="s">
         <v>106</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>97</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>80</v>
       </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
       <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="G78" t="s">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78" t="s">
         <v>111</v>
       </c>
-      <c r="H78">
+      <c r="I78">
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>59</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
         <v>97</v>
       </c>
-      <c r="C79" t="s">
-        <v>82</v>
-      </c>
       <c r="D79" t="s">
+        <v>82</v>
+      </c>
+      <c r="E79" t="s">
         <v>106</v>
       </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
       <c r="F79">
-        <v>3</v>
-      </c>
-      <c r="G79" t="s">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>3</v>
+      </c>
+      <c r="H79" t="s">
         <v>85</v>
       </c>
-      <c r="H79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>59</v>
       </c>
-      <c r="B80" t="s">
-        <v>82</v>
+      <c r="B80">
+        <v>7</v>
       </c>
       <c r="C80" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" t="s">
         <v>86</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>97</v>
       </c>
-      <c r="E80">
-        <v>2</v>
-      </c>
       <c r="F80">
-        <v>3</v>
-      </c>
-      <c r="H80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>3</v>
+      </c>
+      <c r="I80">
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>59</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81">
+        <v>8</v>
+      </c>
+      <c r="C81" t="s">
         <v>86</v>
       </c>
-      <c r="C81" t="s">
-        <v>82</v>
-      </c>
       <c r="D81" t="s">
         <v>82</v>
       </c>
-      <c r="E81">
-        <v>0</v>
+      <c r="E81" t="s">
+        <v>82</v>
       </c>
       <c r="F81">
-        <v>3</v>
-      </c>
-      <c r="G81" t="s">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>3</v>
+      </c>
+      <c r="H81" t="s">
         <v>92</v>
       </c>
-      <c r="H81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>59</v>
       </c>
-      <c r="B82" t="s">
-        <v>82</v>
+      <c r="B82">
+        <v>9</v>
       </c>
       <c r="C82" t="s">
         <v>82</v>
       </c>
       <c r="D82" t="s">
+        <v>82</v>
+      </c>
+      <c r="E82" t="s">
         <v>86</v>
       </c>
-      <c r="E82">
-        <v>2</v>
-      </c>
       <c r="F82">
-        <v>3</v>
-      </c>
-      <c r="H82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="G82">
+        <v>3</v>
+      </c>
+      <c r="I82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>59</v>
       </c>
-      <c r="B83" t="s">
-        <v>82</v>
+      <c r="B83">
+        <v>10</v>
       </c>
       <c r="C83" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" t="s">
         <v>107</v>
       </c>
-      <c r="D83" t="s">
-        <v>82</v>
-      </c>
-      <c r="E83">
-        <v>1</v>
+      <c r="E83" t="s">
+        <v>82</v>
       </c>
       <c r="F83">
-        <v>2</v>
-      </c>
-      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>2</v>
+      </c>
+      <c r="I83">
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>59</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
         <v>107</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>88</v>
       </c>
-      <c r="D84" t="s">
-        <v>82</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
+      <c r="E84" t="s">
+        <v>82</v>
       </c>
       <c r="F84">
-        <v>2</v>
-      </c>
-      <c r="G84" t="s">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>2</v>
+      </c>
+      <c r="H84" t="s">
         <v>113</v>
       </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>59</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85">
+        <v>12</v>
+      </c>
+      <c r="C85" t="s">
         <v>88</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>100</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>107</v>
       </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
       <c r="F85">
-        <v>2</v>
-      </c>
-      <c r="G85" t="s">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>2</v>
+      </c>
+      <c r="H85" t="s">
         <v>113</v>
       </c>
-      <c r="H85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>59</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
         <v>100</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>88</v>
       </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
       <c r="F86">
-        <v>2</v>
-      </c>
-      <c r="G86" t="s">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>2</v>
+      </c>
+      <c r="H86" t="s">
         <v>113</v>
       </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>60</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2">
+        <v>0</v>
+      </c>
+      <c r="C87" t="s">
         <v>78</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>96</v>
       </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
       <c r="F87">
         <v>0</v>
       </c>
-      <c r="H87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>60</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
         <v>96</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>80</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>78</v>
       </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
       <c r="F88">
-        <v>1</v>
-      </c>
-      <c r="G88" t="s">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88" t="s">
         <v>101</v>
       </c>
-      <c r="H88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>60</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2">
+        <v>2</v>
+      </c>
+      <c r="C89" t="s">
         <v>80</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>95</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>96</v>
       </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
       <c r="F89">
-        <v>1</v>
-      </c>
-      <c r="G89" t="s">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
         <v>116</v>
       </c>
-      <c r="H89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>60</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2">
+        <v>3</v>
+      </c>
+      <c r="C90" t="s">
         <v>95</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>97</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>80</v>
       </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
       <c r="F90">
-        <v>1</v>
-      </c>
-      <c r="G90" t="s">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
         <v>90</v>
       </c>
-      <c r="H90">
+      <c r="I90">
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>60</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
         <v>97</v>
       </c>
-      <c r="C91" t="s">
-        <v>82</v>
-      </c>
       <c r="D91" t="s">
+        <v>82</v>
+      </c>
+      <c r="E91" t="s">
         <v>95</v>
       </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
       <c r="F91">
-        <v>2</v>
-      </c>
-      <c r="G91" t="s">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+      <c r="H91" t="s">
         <v>85</v>
       </c>
-      <c r="H91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>60</v>
       </c>
-      <c r="B92" t="s">
-        <v>82</v>
+      <c r="B92" s="2">
+        <v>5</v>
       </c>
       <c r="C92" t="s">
+        <v>82</v>
+      </c>
+      <c r="D92" t="s">
         <v>114</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>97</v>
       </c>
-      <c r="E92">
-        <v>2</v>
-      </c>
       <c r="F92">
-        <v>3</v>
-      </c>
-      <c r="H92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="G92">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>60</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
         <v>114</v>
       </c>
-      <c r="C93" t="s">
-        <v>82</v>
-      </c>
       <c r="D93" t="s">
         <v>82</v>
       </c>
-      <c r="E93">
-        <v>0</v>
+      <c r="E93" t="s">
+        <v>82</v>
       </c>
       <c r="F93">
-        <v>2</v>
-      </c>
-      <c r="G93" t="s">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>2</v>
+      </c>
+      <c r="H93" t="s">
         <v>92</v>
       </c>
-      <c r="H93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>60</v>
       </c>
-      <c r="B94" t="s">
-        <v>82</v>
+      <c r="B94" s="2">
+        <v>7</v>
       </c>
       <c r="C94" t="s">
         <v>82</v>
       </c>
       <c r="D94" t="s">
+        <v>82</v>
+      </c>
+      <c r="E94" t="s">
         <v>114</v>
       </c>
-      <c r="E94">
-        <v>2</v>
-      </c>
       <c r="F94">
         <v>2</v>
       </c>
-      <c r="H94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G94">
+        <v>2</v>
+      </c>
+      <c r="I94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>60</v>
       </c>
-      <c r="B95" t="s">
-        <v>82</v>
+      <c r="B95" s="2">
+        <v>8</v>
       </c>
       <c r="C95" t="s">
+        <v>82</v>
+      </c>
+      <c r="D95" t="s">
         <v>107</v>
       </c>
-      <c r="D95" t="s">
-        <v>82</v>
-      </c>
-      <c r="E95">
-        <v>1</v>
+      <c r="E95" t="s">
+        <v>82</v>
       </c>
       <c r="F95">
-        <v>2</v>
-      </c>
-      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>2</v>
+      </c>
+      <c r="I95">
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>60</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s">
         <v>107</v>
       </c>
-      <c r="D96" t="s">
-        <v>82</v>
-      </c>
-      <c r="E96">
-        <v>0</v>
+      <c r="E96" t="s">
+        <v>82</v>
       </c>
       <c r="F96">
-        <v>1</v>
-      </c>
-      <c r="G96" t="s">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96" t="s">
         <v>103</v>
       </c>
-      <c r="H96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>61</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="2">
+        <v>0</v>
+      </c>
+      <c r="C97" t="s">
         <v>78</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>104</v>
       </c>
-      <c r="E97">
-        <v>0</v>
-      </c>
       <c r="F97">
         <v>0</v>
       </c>
-      <c r="H97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>61</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
         <v>104</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>105</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>78</v>
       </c>
-      <c r="E98">
-        <v>0</v>
-      </c>
       <c r="F98">
-        <v>1</v>
-      </c>
-      <c r="G98" t="s">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98" t="s">
         <v>108</v>
       </c>
-      <c r="H98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>61</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="2">
+        <v>2</v>
+      </c>
+      <c r="C99" t="s">
         <v>105</v>
       </c>
-      <c r="C99" t="s">
-        <v>82</v>
-      </c>
       <c r="D99" t="s">
+        <v>82</v>
+      </c>
+      <c r="E99" t="s">
         <v>104</v>
       </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
       <c r="F99">
-        <v>1</v>
-      </c>
-      <c r="G99" t="s">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99" t="s">
         <v>117</v>
       </c>
-      <c r="H99">
+      <c r="I99">
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>61</v>
       </c>
-      <c r="B100" t="s">
-        <v>82</v>
+      <c r="B100" s="2">
+        <v>3</v>
       </c>
       <c r="C100" t="s">
+        <v>82</v>
+      </c>
+      <c r="D100" t="s">
         <v>80</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>105</v>
       </c>
-      <c r="E100">
-        <v>1</v>
-      </c>
       <c r="F100">
         <v>1</v>
       </c>
-      <c r="H100">
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="I100">
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>61</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="2">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
         <v>80</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>106</v>
       </c>
-      <c r="D101" t="s">
-        <v>82</v>
-      </c>
-      <c r="E101">
-        <v>1</v>
+      <c r="E101" t="s">
+        <v>82</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
-      <c r="H101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>61</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="2">
+        <v>5</v>
+      </c>
+      <c r="C102" t="s">
         <v>106</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>97</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>80</v>
       </c>
-      <c r="E102">
-        <v>0</v>
-      </c>
       <c r="F102">
-        <v>1</v>
-      </c>
-      <c r="G102" t="s">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102" t="s">
         <v>111</v>
       </c>
-      <c r="H102">
+      <c r="I102">
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>61</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="2">
+        <v>6</v>
+      </c>
+      <c r="C103" t="s">
         <v>97</v>
       </c>
-      <c r="C103" t="s">
-        <v>82</v>
-      </c>
       <c r="D103" t="s">
+        <v>82</v>
+      </c>
+      <c r="E103" t="s">
         <v>106</v>
       </c>
-      <c r="E103">
-        <v>0</v>
-      </c>
       <c r="F103">
-        <v>3</v>
-      </c>
-      <c r="G103" t="s">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>3</v>
+      </c>
+      <c r="H103" t="s">
         <v>85</v>
       </c>
-      <c r="H103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>61</v>
       </c>
-      <c r="B104" t="s">
-        <v>82</v>
+      <c r="B104" s="2">
+        <v>7</v>
       </c>
       <c r="C104" t="s">
+        <v>82</v>
+      </c>
+      <c r="D104" t="s">
         <v>114</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>97</v>
       </c>
-      <c r="E104">
-        <v>2</v>
-      </c>
       <c r="F104">
-        <v>3</v>
-      </c>
-      <c r="H104">
+        <v>2</v>
+      </c>
+      <c r="G104">
+        <v>3</v>
+      </c>
+      <c r="I104">
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>61</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="2">
+        <v>8</v>
+      </c>
+      <c r="C105" t="s">
         <v>114</v>
       </c>
-      <c r="C105" t="s">
-        <v>82</v>
-      </c>
       <c r="D105" t="s">
         <v>82</v>
       </c>
-      <c r="E105">
-        <v>0</v>
+      <c r="E105" t="s">
+        <v>82</v>
       </c>
       <c r="F105">
-        <v>2</v>
-      </c>
-      <c r="G105" t="s">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>2</v>
+      </c>
+      <c r="H105" t="s">
         <v>92</v>
       </c>
-      <c r="H105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>61</v>
       </c>
-      <c r="B106" t="s">
-        <v>82</v>
+      <c r="B106" s="2">
+        <v>9</v>
       </c>
       <c r="C106" t="s">
         <v>82</v>
       </c>
       <c r="D106" t="s">
+        <v>82</v>
+      </c>
+      <c r="E106" t="s">
         <v>114</v>
       </c>
-      <c r="E106">
-        <v>2</v>
-      </c>
       <c r="F106">
         <v>2</v>
       </c>
-      <c r="H106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G106">
+        <v>2</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>61</v>
       </c>
-      <c r="B107" t="s">
-        <v>82</v>
+      <c r="B107" s="2">
+        <v>10</v>
       </c>
       <c r="C107" t="s">
+        <v>82</v>
+      </c>
+      <c r="D107" t="s">
         <v>107</v>
       </c>
-      <c r="D107" t="s">
-        <v>82</v>
-      </c>
-      <c r="E107">
-        <v>1</v>
+      <c r="E107" t="s">
+        <v>82</v>
       </c>
       <c r="F107">
-        <v>2</v>
-      </c>
-      <c r="H107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G107">
+        <v>2</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>61</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="2">
+        <v>11</v>
+      </c>
+      <c r="C108" t="s">
         <v>107</v>
       </c>
-      <c r="D108" t="s">
-        <v>82</v>
-      </c>
-      <c r="E108">
-        <v>0</v>
+      <c r="E108" t="s">
+        <v>82</v>
       </c>
       <c r="F108">
-        <v>2</v>
-      </c>
-      <c r="G108" t="s">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>2</v>
+      </c>
+      <c r="H108" t="s">
         <v>113</v>
       </c>
-      <c r="H108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>62</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="2">
+        <v>0</v>
+      </c>
+      <c r="C109" t="s">
         <v>78</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>96</v>
       </c>
-      <c r="E109">
-        <v>0</v>
-      </c>
       <c r="F109">
         <v>0</v>
       </c>
-      <c r="H109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>62</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="2">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
         <v>96</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>80</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>78</v>
       </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
       <c r="F110">
-        <v>1</v>
-      </c>
-      <c r="G110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110" t="s">
         <v>101</v>
       </c>
-      <c r="H110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>62</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="2">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
         <v>80</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>95</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>96</v>
       </c>
-      <c r="E111">
-        <v>0</v>
-      </c>
       <c r="F111">
-        <v>1</v>
-      </c>
-      <c r="G111" t="s">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111" t="s">
         <v>116</v>
       </c>
-      <c r="H111">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>62</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="2">
+        <v>3</v>
+      </c>
+      <c r="C112" t="s">
         <v>95</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>97</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>80</v>
       </c>
-      <c r="E112">
-        <v>0</v>
-      </c>
       <c r="F112">
-        <v>1</v>
-      </c>
-      <c r="G112" t="s">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112" t="s">
         <v>90</v>
       </c>
-      <c r="H112">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I112">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>62</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="2">
+        <v>4</v>
+      </c>
+      <c r="C113" t="s">
         <v>97</v>
       </c>
-      <c r="C113" t="s">
-        <v>82</v>
-      </c>
       <c r="D113" t="s">
+        <v>82</v>
+      </c>
+      <c r="E113" t="s">
         <v>95</v>
       </c>
-      <c r="E113">
-        <v>0</v>
-      </c>
       <c r="F113">
-        <v>2</v>
-      </c>
-      <c r="G113" t="s">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>2</v>
+      </c>
+      <c r="H113" t="s">
         <v>85</v>
       </c>
-      <c r="H113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>62</v>
       </c>
-      <c r="B114" t="s">
-        <v>82</v>
+      <c r="B114" s="2">
+        <v>5</v>
       </c>
       <c r="C114" t="s">
+        <v>82</v>
+      </c>
+      <c r="D114" t="s">
         <v>98</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>97</v>
       </c>
-      <c r="E114">
-        <v>2</v>
-      </c>
       <c r="F114">
         <v>2</v>
       </c>
-      <c r="H114">
+      <c r="G114">
+        <v>2</v>
+      </c>
+      <c r="I114">
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>62</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="2">
+        <v>6</v>
+      </c>
+      <c r="C115" t="s">
         <v>98</v>
       </c>
-      <c r="C115" t="s">
-        <v>82</v>
-      </c>
       <c r="D115" t="s">
         <v>82</v>
       </c>
-      <c r="E115">
-        <v>0</v>
+      <c r="E115" t="s">
+        <v>82</v>
       </c>
       <c r="F115">
-        <v>2</v>
-      </c>
-      <c r="G115" t="s">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>2</v>
+      </c>
+      <c r="H115" t="s">
         <v>92</v>
       </c>
-      <c r="H115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>62</v>
       </c>
-      <c r="B116" t="s">
-        <v>82</v>
+      <c r="B116" s="2">
+        <v>7</v>
       </c>
       <c r="C116" t="s">
+        <v>82</v>
+      </c>
+      <c r="D116" t="s">
         <v>100</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>98</v>
       </c>
-      <c r="E116">
-        <v>1</v>
-      </c>
       <c r="F116">
         <v>1</v>
       </c>
-      <c r="H116">
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="I116">
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>62</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="2">
+        <v>8</v>
+      </c>
+      <c r="C117" t="s">
         <v>100</v>
       </c>
-      <c r="D117" t="s">
-        <v>82</v>
-      </c>
-      <c r="E117">
-        <v>0</v>
+      <c r="E117" t="s">
+        <v>82</v>
       </c>
       <c r="F117">
-        <v>1</v>
-      </c>
-      <c r="G117" t="s">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117" t="s">
         <v>103</v>
       </c>
-      <c r="H117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>63</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="2">
+        <v>0</v>
+      </c>
+      <c r="C118" t="s">
         <v>78</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>104</v>
       </c>
-      <c r="E118">
-        <v>0</v>
-      </c>
       <c r="F118">
         <v>0</v>
       </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>63</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="2">
+        <v>1</v>
+      </c>
+      <c r="C119" t="s">
         <v>104</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>105</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>78</v>
       </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
       <c r="F119">
-        <v>1</v>
-      </c>
-      <c r="G119" t="s">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119" t="s">
         <v>101</v>
       </c>
-      <c r="H119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>63</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="2">
+        <v>2</v>
+      </c>
+      <c r="C120" t="s">
         <v>105</v>
       </c>
-      <c r="C120" t="s">
-        <v>82</v>
-      </c>
       <c r="D120" t="s">
+        <v>82</v>
+      </c>
+      <c r="E120" t="s">
         <v>104</v>
       </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
       <c r="F120">
-        <v>1</v>
-      </c>
-      <c r="G120" t="s">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120" t="s">
         <v>109</v>
       </c>
-      <c r="H120">
+      <c r="I120">
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>63</v>
       </c>
-      <c r="B121" t="s">
-        <v>82</v>
+      <c r="B121" s="2">
+        <v>3</v>
       </c>
       <c r="C121" t="s">
+        <v>82</v>
+      </c>
+      <c r="D121" t="s">
         <v>80</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>105</v>
       </c>
-      <c r="E121">
-        <v>1</v>
-      </c>
       <c r="F121">
         <v>1</v>
       </c>
-      <c r="H121">
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="I121">
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>63</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="2">
+        <v>4</v>
+      </c>
+      <c r="C122" t="s">
         <v>80</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>106</v>
       </c>
-      <c r="D122" t="s">
-        <v>82</v>
-      </c>
-      <c r="E122">
-        <v>1</v>
+      <c r="E122" t="s">
+        <v>82</v>
       </c>
       <c r="F122">
         <v>1</v>
       </c>
-      <c r="H122">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>63</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="2">
+        <v>5</v>
+      </c>
+      <c r="C123" t="s">
         <v>106</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>97</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
         <v>80</v>
       </c>
-      <c r="E123">
-        <v>0</v>
-      </c>
       <c r="F123">
-        <v>1</v>
-      </c>
-      <c r="G123" t="s">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="H123" t="s">
         <v>111</v>
       </c>
-      <c r="H123">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I123">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>63</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="2">
+        <v>6</v>
+      </c>
+      <c r="C124" t="s">
         <v>97</v>
       </c>
-      <c r="C124" t="s">
-        <v>82</v>
-      </c>
       <c r="D124" t="s">
+        <v>82</v>
+      </c>
+      <c r="E124" t="s">
         <v>106</v>
       </c>
-      <c r="E124">
-        <v>0</v>
-      </c>
       <c r="F124">
-        <v>3</v>
-      </c>
-      <c r="G124" t="s">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>3</v>
+      </c>
+      <c r="H124" t="s">
         <v>85</v>
       </c>
-      <c r="H124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>63</v>
       </c>
-      <c r="B125" t="s">
-        <v>82</v>
+      <c r="B125" s="2">
+        <v>7</v>
       </c>
       <c r="C125" t="s">
+        <v>82</v>
+      </c>
+      <c r="D125" t="s">
         <v>86</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>97</v>
       </c>
-      <c r="E125">
-        <v>2</v>
-      </c>
       <c r="F125">
-        <v>3</v>
-      </c>
-      <c r="H125">
+        <v>2</v>
+      </c>
+      <c r="G125">
+        <v>3</v>
+      </c>
+      <c r="I125">
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>63</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="2">
+        <v>8</v>
+      </c>
+      <c r="C126" t="s">
         <v>86</v>
       </c>
-      <c r="C126" t="s">
-        <v>82</v>
-      </c>
       <c r="D126" t="s">
         <v>82</v>
       </c>
-      <c r="E126">
-        <v>0</v>
+      <c r="E126" t="s">
+        <v>82</v>
       </c>
       <c r="F126">
-        <v>3</v>
-      </c>
-      <c r="G126" t="s">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>3</v>
+      </c>
+      <c r="H126" t="s">
         <v>92</v>
       </c>
-      <c r="H126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>63</v>
       </c>
-      <c r="B127" t="s">
-        <v>82</v>
+      <c r="B127" s="2">
+        <v>9</v>
       </c>
       <c r="C127" t="s">
         <v>82</v>
       </c>
       <c r="D127" t="s">
+        <v>82</v>
+      </c>
+      <c r="E127" t="s">
         <v>86</v>
       </c>
-      <c r="E127">
-        <v>2</v>
-      </c>
       <c r="F127">
-        <v>3</v>
-      </c>
-      <c r="H127">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="G127">
+        <v>3</v>
+      </c>
+      <c r="I127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>63</v>
       </c>
-      <c r="B128" t="s">
-        <v>82</v>
+      <c r="B128" s="2">
+        <v>10</v>
       </c>
       <c r="C128" t="s">
+        <v>82</v>
+      </c>
+      <c r="D128" t="s">
         <v>107</v>
       </c>
-      <c r="D128" t="s">
-        <v>82</v>
-      </c>
-      <c r="E128">
-        <v>1</v>
+      <c r="E128" t="s">
+        <v>82</v>
       </c>
       <c r="F128">
-        <v>2</v>
-      </c>
-      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>2</v>
+      </c>
+      <c r="I128">
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>63</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="2">
+        <v>11</v>
+      </c>
+      <c r="C129" t="s">
         <v>107</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
         <v>88</v>
       </c>
-      <c r="D129" t="s">
-        <v>82</v>
-      </c>
-      <c r="E129">
-        <v>0</v>
+      <c r="E129" t="s">
+        <v>82</v>
       </c>
       <c r="F129">
-        <v>2</v>
-      </c>
-      <c r="G129" t="s">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>2</v>
+      </c>
+      <c r="H129" t="s">
         <v>113</v>
       </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>63</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="2">
+        <v>12</v>
+      </c>
+      <c r="C130" t="s">
         <v>88</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
         <v>100</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
         <v>107</v>
       </c>
-      <c r="E130">
-        <v>0</v>
-      </c>
       <c r="F130">
-        <v>2</v>
-      </c>
-      <c r="G130" t="s">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>2</v>
+      </c>
+      <c r="H130" t="s">
         <v>113</v>
       </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>63</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="2">
+        <v>13</v>
+      </c>
+      <c r="C131" t="s">
         <v>100</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
         <v>88</v>
       </c>
-      <c r="E131">
-        <v>0</v>
-      </c>
       <c r="F131">
-        <v>2</v>
-      </c>
-      <c r="G131" t="s">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>2</v>
+      </c>
+      <c r="H131" t="s">
         <v>113</v>
       </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>64</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="2">
+        <v>0</v>
+      </c>
+      <c r="C132" t="s">
         <v>78</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>104</v>
       </c>
-      <c r="E132">
-        <v>0</v>
-      </c>
       <c r="F132">
         <v>0</v>
       </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>64</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="2">
+        <v>1</v>
+      </c>
+      <c r="C133" t="s">
         <v>104</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
         <v>105</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
         <v>78</v>
       </c>
-      <c r="E133">
-        <v>0</v>
-      </c>
       <c r="F133">
-        <v>1</v>
-      </c>
-      <c r="G133" t="s">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133" t="s">
         <v>108</v>
       </c>
-      <c r="H133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>64</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="2">
+        <v>2</v>
+      </c>
+      <c r="C134" t="s">
         <v>105</v>
       </c>
-      <c r="C134" t="s">
-        <v>82</v>
-      </c>
       <c r="D134" t="s">
+        <v>82</v>
+      </c>
+      <c r="E134" t="s">
         <v>104</v>
       </c>
-      <c r="E134">
-        <v>0</v>
-      </c>
       <c r="F134">
-        <v>1</v>
-      </c>
-      <c r="G134" t="s">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134" t="s">
         <v>117</v>
       </c>
-      <c r="H134">
+      <c r="I134">
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>64</v>
       </c>
-      <c r="B135" t="s">
-        <v>82</v>
+      <c r="B135" s="2">
+        <v>3</v>
       </c>
       <c r="C135" t="s">
+        <v>82</v>
+      </c>
+      <c r="D135" t="s">
         <v>80</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
         <v>105</v>
       </c>
-      <c r="E135">
-        <v>1</v>
-      </c>
       <c r="F135">
         <v>1</v>
       </c>
-      <c r="H135">
+      <c r="G135">
+        <v>1</v>
+      </c>
+      <c r="I135">
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>64</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="2">
+        <v>4</v>
+      </c>
+      <c r="C136" t="s">
         <v>80</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
         <v>106</v>
       </c>
-      <c r="D136" t="s">
-        <v>82</v>
-      </c>
-      <c r="E136">
-        <v>1</v>
+      <c r="E136" t="s">
+        <v>82</v>
       </c>
       <c r="F136">
         <v>1</v>
       </c>
-      <c r="H136">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>64</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="2">
+        <v>5</v>
+      </c>
+      <c r="C137" t="s">
         <v>106</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
         <v>97</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>80</v>
       </c>
-      <c r="E137">
-        <v>0</v>
-      </c>
       <c r="F137">
-        <v>1</v>
-      </c>
-      <c r="G137" t="s">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137" t="s">
         <v>111</v>
       </c>
-      <c r="H137">
+      <c r="I137">
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>64</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="2">
+        <v>6</v>
+      </c>
+      <c r="C138" t="s">
         <v>97</v>
       </c>
-      <c r="C138" t="s">
-        <v>82</v>
-      </c>
       <c r="D138" t="s">
+        <v>82</v>
+      </c>
+      <c r="E138" t="s">
         <v>106</v>
       </c>
-      <c r="E138">
-        <v>0</v>
-      </c>
       <c r="F138">
-        <v>3</v>
-      </c>
-      <c r="G138" t="s">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>3</v>
+      </c>
+      <c r="H138" t="s">
         <v>85</v>
       </c>
-      <c r="H138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>64</v>
       </c>
-      <c r="B139" t="s">
-        <v>82</v>
+      <c r="B139" s="2">
+        <v>7</v>
       </c>
       <c r="C139" t="s">
+        <v>82</v>
+      </c>
+      <c r="D139" t="s">
         <v>114</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>97</v>
       </c>
-      <c r="E139">
-        <v>2</v>
-      </c>
       <c r="F139">
-        <v>3</v>
-      </c>
-      <c r="H139">
+        <v>2</v>
+      </c>
+      <c r="G139">
+        <v>3</v>
+      </c>
+      <c r="I139">
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>64</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="2">
+        <v>8</v>
+      </c>
+      <c r="C140" t="s">
         <v>114</v>
       </c>
-      <c r="C140" t="s">
-        <v>82</v>
-      </c>
       <c r="D140" t="s">
         <v>82</v>
       </c>
-      <c r="E140">
-        <v>0</v>
+      <c r="E140" t="s">
+        <v>82</v>
       </c>
       <c r="F140">
-        <v>2</v>
-      </c>
-      <c r="G140" t="s">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>2</v>
+      </c>
+      <c r="H140" t="s">
         <v>92</v>
       </c>
-      <c r="H140">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>64</v>
       </c>
-      <c r="B141" t="s">
-        <v>82</v>
+      <c r="B141" s="2">
+        <v>9</v>
       </c>
       <c r="C141" t="s">
         <v>82</v>
       </c>
       <c r="D141" t="s">
+        <v>82</v>
+      </c>
+      <c r="E141" t="s">
         <v>114</v>
       </c>
-      <c r="E141">
-        <v>2</v>
-      </c>
       <c r="F141">
         <v>2</v>
       </c>
-      <c r="H141">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G141">
+        <v>2</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>64</v>
       </c>
-      <c r="B142" t="s">
-        <v>82</v>
+      <c r="B142" s="2">
+        <v>10</v>
       </c>
       <c r="C142" t="s">
+        <v>82</v>
+      </c>
+      <c r="D142" t="s">
         <v>107</v>
       </c>
-      <c r="D142" t="s">
-        <v>82</v>
-      </c>
-      <c r="E142">
-        <v>1</v>
+      <c r="E142" t="s">
+        <v>82</v>
       </c>
       <c r="F142">
-        <v>2</v>
-      </c>
-      <c r="H142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G142">
+        <v>2</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>64</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="2">
+        <v>11</v>
+      </c>
+      <c r="C143" t="s">
         <v>107</v>
       </c>
-      <c r="D143" t="s">
-        <v>82</v>
-      </c>
-      <c r="E143">
-        <v>0</v>
+      <c r="E143" t="s">
+        <v>82</v>
       </c>
       <c r="F143">
-        <v>2</v>
-      </c>
-      <c r="G143" t="s">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>2</v>
+      </c>
+      <c r="H143" t="s">
         <v>113</v>
       </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B144" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 

--- a/ontology/v2.01/cellfie_import.xlsx
+++ b/ontology/v2.01/cellfie_import.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurasla/Documents/GitHub/bedreflyt/ontology/v2.01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A97D91-6CDA-054F-B3C3-276A6D25A74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA80A41-341A-CE44-BADC-D62C22D9B3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="1220" windowWidth="44580" windowHeight="24560" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
+    <workbookView xWindow="6300" yWindow="1220" windowWidth="61860" windowHeight="24360" activeTab="1" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
   </bookViews>
   <sheets>
     <sheet name="TreatmentJourneys" sheetId="1" r:id="rId1"/>
     <sheet name="Tasks" sheetId="2" r:id="rId2"/>
-    <sheet name="MonitoringCategory" sheetId="9" r:id="rId3"/>
-    <sheet name="City" sheetId="3" r:id="rId4"/>
-    <sheet name="Hospital" sheetId="4" r:id="rId5"/>
-    <sheet name="Floor" sheetId="5" r:id="rId6"/>
-    <sheet name="Ward" sheetId="6" r:id="rId7"/>
-    <sheet name="TreatingRoom" sheetId="7" r:id="rId8"/>
-    <sheet name="Bathroom" sheetId="8" r:id="rId9"/>
+    <sheet name="Task-list" sheetId="10" r:id="rId3"/>
+    <sheet name="MonitoringCategory" sheetId="9" r:id="rId4"/>
+    <sheet name="City" sheetId="3" r:id="rId5"/>
+    <sheet name="Hospital" sheetId="4" r:id="rId6"/>
+    <sheet name="Floor" sheetId="5" r:id="rId7"/>
+    <sheet name="Ward" sheetId="6" r:id="rId8"/>
+    <sheet name="TreatingRoom" sheetId="7" r:id="rId9"/>
+    <sheet name="Bathroom" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="267">
   <si>
     <t>DIAGNOSIS</t>
   </si>
@@ -406,6 +407,444 @@
   </si>
   <si>
     <t>TotalStepNs</t>
+  </si>
+  <si>
+    <t>EXSTEP</t>
+  </si>
+  <si>
+    <t>EXSTEPF</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>S06.5_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>D32.5_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>M50.1_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_14</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_12</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_12</t>
+  </si>
+  <si>
+    <t>S06.5_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>D32.5_Standard_STEP_10</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_13</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_11</t>
+  </si>
+  <si>
+    <t>M50.1_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_13</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_11</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_10</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_11</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_12</t>
+  </si>
+  <si>
+    <t>I60.0_Standard_STEP_13</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_10</t>
+  </si>
+  <si>
+    <t>I60.1_Standard_STEP_11</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>M50.0_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_10</t>
+  </si>
+  <si>
+    <t>G91.2_Standard_STEP_11</t>
+  </si>
+  <si>
+    <t>S06.5_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>S06.5_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>S06.5_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>S06.5_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>S06.5_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>S06.5_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>S06.5_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_0</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>D35.2_Standard_STEP_10</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_10</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_11</t>
+  </si>
+  <si>
+    <t>I67.1_Standard_STEP_12</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>D32.0_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>C71.2_Standard_STEP_10</t>
+  </si>
+  <si>
+    <t>M50.1_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>M50.1_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>M50.1_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>M50.1_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>M50.1_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>M50.1_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>M50.1_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_10</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_11</t>
+  </si>
+  <si>
+    <t>G50.0_Standard_STEP_12</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_1</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_2</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_3</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_4</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_5</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_6</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_7</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_8</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_9</t>
+  </si>
+  <si>
+    <t>C71.3_Standard_STEP_10</t>
   </si>
 </sst>
 </file>
@@ -800,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B973482-F93F-2340-91C4-4A18BF01CE10}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -810,9 +1249,12 @@
     <col min="5" max="5" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,8 +1279,14 @@
       <c r="H1" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -863,8 +1311,14 @@
       <c r="H2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -889,8 +1343,14 @@
       <c r="H3">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -915,8 +1375,14 @@
       <c r="H4">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" t="s">
+        <v>125</v>
+      </c>
+      <c r="J4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -941,8 +1407,14 @@
       <c r="H5">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -967,8 +1439,14 @@
       <c r="H6">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -993,8 +1471,14 @@
       <c r="H7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1019,8 +1503,14 @@
       <c r="H8">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8" t="s">
+        <v>129</v>
+      </c>
+      <c r="J8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -1045,8 +1535,14 @@
       <c r="H9">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -1071,8 +1567,14 @@
       <c r="H10">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1097,8 +1599,14 @@
       <c r="H11">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>132</v>
+      </c>
+      <c r="J11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -1123,8 +1631,14 @@
       <c r="H12">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>133</v>
+      </c>
+      <c r="J12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1148,6 +1662,66 @@
       </c>
       <c r="H13">
         <v>11</v>
+      </c>
+      <c r="I13" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53EB7CAF-F72D-D848-9389-E9B506E330DC}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1161,7 +1735,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.1640625" customWidth="1"/>
     <col min="3" max="5" width="24.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
@@ -1203,8 +1777,8 @@
       <c r="A2" t="s">
         <v>53</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" t="s">
+        <v>123</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -1226,8 +1800,8 @@
       <c r="A3" t="s">
         <v>53</v>
       </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" t="s">
+        <v>147</v>
       </c>
       <c r="C3" t="s">
         <v>79</v>
@@ -1255,8 +1829,8 @@
       <c r="A4" t="s">
         <v>53</v>
       </c>
-      <c r="B4">
-        <v>2</v>
+      <c r="B4" t="s">
+        <v>148</v>
       </c>
       <c r="C4" t="s">
         <v>80</v>
@@ -1281,8 +1855,8 @@
       <c r="A5" t="s">
         <v>53</v>
       </c>
-      <c r="B5">
-        <v>3</v>
+      <c r="B5" t="s">
+        <v>149</v>
       </c>
       <c r="C5" t="s">
         <v>81</v>
@@ -1310,8 +1884,8 @@
       <c r="A6" t="s">
         <v>53</v>
       </c>
-      <c r="B6">
-        <v>4</v>
+      <c r="B6" t="s">
+        <v>150</v>
       </c>
       <c r="C6" t="s">
         <v>82</v>
@@ -1336,8 +1910,8 @@
       <c r="A7" t="s">
         <v>53</v>
       </c>
-      <c r="B7">
-        <v>5</v>
+      <c r="B7" t="s">
+        <v>151</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
@@ -1365,8 +1939,8 @@
       <c r="A8" t="s">
         <v>53</v>
       </c>
-      <c r="B8">
-        <v>6</v>
+      <c r="B8" t="s">
+        <v>152</v>
       </c>
       <c r="C8" t="s">
         <v>84</v>
@@ -1394,8 +1968,8 @@
       <c r="A9" t="s">
         <v>53</v>
       </c>
-      <c r="B9">
-        <v>7</v>
+      <c r="B9" t="s">
+        <v>153</v>
       </c>
       <c r="C9" t="s">
         <v>85</v>
@@ -1423,8 +1997,8 @@
       <c r="A10" t="s">
         <v>53</v>
       </c>
-      <c r="B10">
-        <v>8</v>
+      <c r="B10" t="s">
+        <v>154</v>
       </c>
       <c r="C10" t="s">
         <v>82</v>
@@ -1449,8 +2023,8 @@
       <c r="A11" t="s">
         <v>53</v>
       </c>
-      <c r="B11">
-        <v>9</v>
+      <c r="B11" t="s">
+        <v>155</v>
       </c>
       <c r="C11" t="s">
         <v>86</v>
@@ -1478,8 +2052,8 @@
       <c r="A12" t="s">
         <v>53</v>
       </c>
-      <c r="B12">
-        <v>10</v>
+      <c r="B12" t="s">
+        <v>156</v>
       </c>
       <c r="C12" t="s">
         <v>82</v>
@@ -1504,8 +2078,8 @@
       <c r="A13" t="s">
         <v>53</v>
       </c>
-      <c r="B13">
-        <v>11</v>
+      <c r="B13" t="s">
+        <v>157</v>
       </c>
       <c r="C13" t="s">
         <v>86</v>
@@ -1533,8 +2107,8 @@
       <c r="A14" t="s">
         <v>53</v>
       </c>
-      <c r="B14">
-        <v>12</v>
+      <c r="B14" t="s">
+        <v>158</v>
       </c>
       <c r="C14" t="s">
         <v>82</v>
@@ -1559,8 +2133,8 @@
       <c r="A15" t="s">
         <v>53</v>
       </c>
-      <c r="B15">
-        <v>13</v>
+      <c r="B15" t="s">
+        <v>159</v>
       </c>
       <c r="C15" t="s">
         <v>87</v>
@@ -1588,8 +2162,8 @@
       <c r="A16" t="s">
         <v>53</v>
       </c>
-      <c r="B16">
-        <v>14</v>
+      <c r="B16" t="s">
+        <v>135</v>
       </c>
       <c r="C16" t="s">
         <v>88</v>
@@ -1614,8 +2188,8 @@
       <c r="A17" t="s">
         <v>54</v>
       </c>
-      <c r="B17">
-        <v>0</v>
+      <c r="B17" t="s">
+        <v>124</v>
       </c>
       <c r="C17" t="s">
         <v>78</v>
@@ -1637,8 +2211,8 @@
       <c r="A18" t="s">
         <v>54</v>
       </c>
-      <c r="B18">
-        <v>1</v>
+      <c r="B18" t="s">
+        <v>160</v>
       </c>
       <c r="C18" t="s">
         <v>79</v>
@@ -1666,8 +2240,8 @@
       <c r="A19" t="s">
         <v>54</v>
       </c>
-      <c r="B19">
-        <v>2</v>
+      <c r="B19" t="s">
+        <v>161</v>
       </c>
       <c r="C19" t="s">
         <v>80</v>
@@ -1692,8 +2266,8 @@
       <c r="A20" t="s">
         <v>54</v>
       </c>
-      <c r="B20">
-        <v>3</v>
+      <c r="B20" t="s">
+        <v>162</v>
       </c>
       <c r="C20" t="s">
         <v>81</v>
@@ -1721,8 +2295,8 @@
       <c r="A21" t="s">
         <v>54</v>
       </c>
-      <c r="B21">
-        <v>4</v>
+      <c r="B21" t="s">
+        <v>163</v>
       </c>
       <c r="C21" t="s">
         <v>95</v>
@@ -1750,8 +2324,8 @@
       <c r="A22" t="s">
         <v>54</v>
       </c>
-      <c r="B22">
-        <v>5</v>
+      <c r="B22" t="s">
+        <v>164</v>
       </c>
       <c r="C22" t="s">
         <v>85</v>
@@ -1779,8 +2353,8 @@
       <c r="A23" t="s">
         <v>54</v>
       </c>
-      <c r="B23">
-        <v>6</v>
+      <c r="B23" t="s">
+        <v>165</v>
       </c>
       <c r="C23" t="s">
         <v>82</v>
@@ -1805,8 +2379,8 @@
       <c r="A24" t="s">
         <v>54</v>
       </c>
-      <c r="B24">
-        <v>7</v>
+      <c r="B24" t="s">
+        <v>166</v>
       </c>
       <c r="C24" t="s">
         <v>86</v>
@@ -1834,8 +2408,8 @@
       <c r="A25" t="s">
         <v>54</v>
       </c>
-      <c r="B25">
-        <v>8</v>
+      <c r="B25" t="s">
+        <v>167</v>
       </c>
       <c r="C25" t="s">
         <v>82</v>
@@ -1860,8 +2434,8 @@
       <c r="A26" t="s">
         <v>54</v>
       </c>
-      <c r="B26">
-        <v>9</v>
+      <c r="B26" t="s">
+        <v>168</v>
       </c>
       <c r="C26" t="s">
         <v>86</v>
@@ -1889,8 +2463,8 @@
       <c r="A27" t="s">
         <v>54</v>
       </c>
-      <c r="B27">
-        <v>10</v>
+      <c r="B27" t="s">
+        <v>169</v>
       </c>
       <c r="C27" t="s">
         <v>82</v>
@@ -1915,8 +2489,8 @@
       <c r="A28" t="s">
         <v>54</v>
       </c>
-      <c r="B28">
-        <v>11</v>
+      <c r="B28" t="s">
+        <v>170</v>
       </c>
       <c r="C28" t="s">
         <v>87</v>
@@ -1944,8 +2518,8 @@
       <c r="A29" t="s">
         <v>54</v>
       </c>
-      <c r="B29">
-        <v>12</v>
+      <c r="B29" t="s">
+        <v>136</v>
       </c>
       <c r="C29" t="s">
         <v>88</v>
@@ -1970,8 +2544,8 @@
       <c r="A30" t="s">
         <v>55</v>
       </c>
-      <c r="B30">
-        <v>0</v>
+      <c r="B30" t="s">
+        <v>125</v>
       </c>
       <c r="C30" t="s">
         <v>78</v>
@@ -1993,8 +2567,8 @@
       <c r="A31" t="s">
         <v>55</v>
       </c>
-      <c r="B31">
-        <v>1</v>
+      <c r="B31" t="s">
+        <v>171</v>
       </c>
       <c r="C31" t="s">
         <v>96</v>
@@ -2022,8 +2596,8 @@
       <c r="A32" t="s">
         <v>55</v>
       </c>
-      <c r="B32">
-        <v>2</v>
+      <c r="B32" t="s">
+        <v>172</v>
       </c>
       <c r="C32" t="s">
         <v>80</v>
@@ -2051,8 +2625,8 @@
       <c r="A33" t="s">
         <v>55</v>
       </c>
-      <c r="B33">
-        <v>3</v>
+      <c r="B33" t="s">
+        <v>173</v>
       </c>
       <c r="C33" t="s">
         <v>80</v>
@@ -2077,8 +2651,8 @@
       <c r="A34" t="s">
         <v>55</v>
       </c>
-      <c r="B34">
-        <v>4</v>
+      <c r="B34" t="s">
+        <v>174</v>
       </c>
       <c r="C34" t="s">
         <v>95</v>
@@ -2106,8 +2680,8 @@
       <c r="A35" t="s">
         <v>55</v>
       </c>
-      <c r="B35">
-        <v>5</v>
+      <c r="B35" t="s">
+        <v>175</v>
       </c>
       <c r="C35" t="s">
         <v>97</v>
@@ -2135,8 +2709,8 @@
       <c r="A36" t="s">
         <v>55</v>
       </c>
-      <c r="B36">
-        <v>6</v>
+      <c r="B36" t="s">
+        <v>176</v>
       </c>
       <c r="C36" t="s">
         <v>82</v>
@@ -2161,8 +2735,8 @@
       <c r="A37" t="s">
         <v>55</v>
       </c>
-      <c r="B37">
-        <v>7</v>
+      <c r="B37" t="s">
+        <v>177</v>
       </c>
       <c r="C37" t="s">
         <v>98</v>
@@ -2190,8 +2764,8 @@
       <c r="A38" t="s">
         <v>55</v>
       </c>
-      <c r="B38">
-        <v>8</v>
+      <c r="B38" t="s">
+        <v>178</v>
       </c>
       <c r="C38" t="s">
         <v>99</v>
@@ -2216,8 +2790,8 @@
       <c r="A39" t="s">
         <v>55</v>
       </c>
-      <c r="B39">
-        <v>9</v>
+      <c r="B39" t="s">
+        <v>137</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -2242,8 +2816,8 @@
       <c r="A40" t="s">
         <v>56</v>
       </c>
-      <c r="B40">
-        <v>0</v>
+      <c r="B40" t="s">
+        <v>126</v>
       </c>
       <c r="C40" t="s">
         <v>78</v>
@@ -2265,8 +2839,8 @@
       <c r="A41" t="s">
         <v>56</v>
       </c>
-      <c r="B41">
-        <v>1</v>
+      <c r="B41" t="s">
+        <v>179</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
@@ -2294,8 +2868,8 @@
       <c r="A42" t="s">
         <v>56</v>
       </c>
-      <c r="B42">
-        <v>2</v>
+      <c r="B42" t="s">
+        <v>180</v>
       </c>
       <c r="C42" t="s">
         <v>105</v>
@@ -2323,8 +2897,8 @@
       <c r="A43" t="s">
         <v>56</v>
       </c>
-      <c r="B43">
-        <v>3</v>
+      <c r="B43" t="s">
+        <v>181</v>
       </c>
       <c r="C43" t="s">
         <v>82</v>
@@ -2352,8 +2926,8 @@
       <c r="A44" t="s">
         <v>56</v>
       </c>
-      <c r="B44">
-        <v>4</v>
+      <c r="B44" t="s">
+        <v>182</v>
       </c>
       <c r="C44" t="s">
         <v>80</v>
@@ -2381,8 +2955,8 @@
       <c r="A45" t="s">
         <v>56</v>
       </c>
-      <c r="B45">
-        <v>5</v>
+      <c r="B45" t="s">
+        <v>183</v>
       </c>
       <c r="C45" t="s">
         <v>106</v>
@@ -2410,8 +2984,8 @@
       <c r="A46" t="s">
         <v>56</v>
       </c>
-      <c r="B46">
-        <v>6</v>
+      <c r="B46" t="s">
+        <v>184</v>
       </c>
       <c r="C46" t="s">
         <v>97</v>
@@ -2439,8 +3013,8 @@
       <c r="A47" t="s">
         <v>56</v>
       </c>
-      <c r="B47">
-        <v>7</v>
+      <c r="B47" t="s">
+        <v>185</v>
       </c>
       <c r="C47" t="s">
         <v>82</v>
@@ -2468,8 +3042,8 @@
       <c r="A48" t="s">
         <v>56</v>
       </c>
-      <c r="B48">
-        <v>8</v>
+      <c r="B48" t="s">
+        <v>186</v>
       </c>
       <c r="C48" t="s">
         <v>86</v>
@@ -2497,8 +3071,8 @@
       <c r="A49" t="s">
         <v>56</v>
       </c>
-      <c r="B49">
-        <v>9</v>
+      <c r="B49" t="s">
+        <v>187</v>
       </c>
       <c r="C49" t="s">
         <v>82</v>
@@ -2526,8 +3100,8 @@
       <c r="A50" t="s">
         <v>56</v>
       </c>
-      <c r="B50">
-        <v>10</v>
+      <c r="B50" t="s">
+        <v>188</v>
       </c>
       <c r="C50" t="s">
         <v>82</v>
@@ -2555,8 +3129,8 @@
       <c r="A51" t="s">
         <v>56</v>
       </c>
-      <c r="B51">
-        <v>11</v>
+      <c r="B51" t="s">
+        <v>189</v>
       </c>
       <c r="C51" t="s">
         <v>107</v>
@@ -2584,8 +3158,8 @@
       <c r="A52" t="s">
         <v>56</v>
       </c>
-      <c r="B52">
-        <v>12</v>
+      <c r="B52" t="s">
+        <v>138</v>
       </c>
       <c r="C52" t="s">
         <v>88</v>
@@ -2610,8 +3184,8 @@
       <c r="A53" t="s">
         <v>57</v>
       </c>
-      <c r="B53">
-        <v>0</v>
+      <c r="B53" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="C53" t="s">
         <v>78</v>
@@ -2633,8 +3207,8 @@
       <c r="A54" t="s">
         <v>57</v>
       </c>
-      <c r="B54">
-        <v>1</v>
+      <c r="B54" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="C54" t="s">
         <v>79</v>
@@ -2662,8 +3236,8 @@
       <c r="A55" t="s">
         <v>57</v>
       </c>
-      <c r="B55">
-        <v>2</v>
+      <c r="B55" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="C55" t="s">
         <v>80</v>
@@ -2688,8 +3262,8 @@
       <c r="A56" t="s">
         <v>57</v>
       </c>
-      <c r="B56">
-        <v>3</v>
+      <c r="B56" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="C56" t="s">
         <v>80</v>
@@ -2714,8 +3288,8 @@
       <c r="A57" t="s">
         <v>57</v>
       </c>
-      <c r="B57">
-        <v>4</v>
+      <c r="B57" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="C57" t="s">
         <v>95</v>
@@ -2743,8 +3317,8 @@
       <c r="A58" t="s">
         <v>57</v>
       </c>
-      <c r="B58">
-        <v>5</v>
+      <c r="B58" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="C58" t="s">
         <v>82</v>
@@ -2769,8 +3343,8 @@
       <c r="A59" t="s">
         <v>57</v>
       </c>
-      <c r="B59">
-        <v>6</v>
+      <c r="B59" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="C59" t="s">
         <v>86</v>
@@ -2798,8 +3372,8 @@
       <c r="A60" t="s">
         <v>57</v>
       </c>
-      <c r="B60">
-        <v>7</v>
+      <c r="B60" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="C60" t="s">
         <v>82</v>
@@ -2824,8 +3398,8 @@
       <c r="A61" t="s">
         <v>57</v>
       </c>
-      <c r="B61">
-        <v>8</v>
+      <c r="B61" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="C61" t="s">
         <v>107</v>
@@ -2850,8 +3424,8 @@
       <c r="A62" t="s">
         <v>115</v>
       </c>
-      <c r="B62">
-        <v>0</v>
+      <c r="B62" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="C62" t="s">
         <v>78</v>
@@ -2873,8 +3447,8 @@
       <c r="A63" t="s">
         <v>115</v>
       </c>
-      <c r="B63">
-        <v>1</v>
+      <c r="B63" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="C63" t="s">
         <v>96</v>
@@ -2902,8 +3476,8 @@
       <c r="A64" t="s">
         <v>115</v>
       </c>
-      <c r="B64">
-        <v>2</v>
+      <c r="B64" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="C64" t="s">
         <v>80</v>
@@ -2931,8 +3505,8 @@
       <c r="A65" t="s">
         <v>115</v>
       </c>
-      <c r="B65">
-        <v>3</v>
+      <c r="B65" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="C65" t="s">
         <v>95</v>
@@ -2960,8 +3534,8 @@
       <c r="A66" t="s">
         <v>115</v>
       </c>
-      <c r="B66">
-        <v>4</v>
+      <c r="B66" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="C66" t="s">
         <v>97</v>
@@ -2989,8 +3563,8 @@
       <c r="A67" t="s">
         <v>115</v>
       </c>
-      <c r="B67">
-        <v>5</v>
+      <c r="B67" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="C67" t="s">
         <v>82</v>
@@ -3015,8 +3589,8 @@
       <c r="A68" t="s">
         <v>115</v>
       </c>
-      <c r="B68">
-        <v>6</v>
+      <c r="B68" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="C68" t="s">
         <v>114</v>
@@ -3044,8 +3618,8 @@
       <c r="A69" t="s">
         <v>115</v>
       </c>
-      <c r="B69">
-        <v>7</v>
+      <c r="B69" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="C69" t="s">
         <v>82</v>
@@ -3070,8 +3644,8 @@
       <c r="A70" t="s">
         <v>115</v>
       </c>
-      <c r="B70">
-        <v>8</v>
+      <c r="B70" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="C70" t="s">
         <v>82</v>
@@ -3096,8 +3670,8 @@
       <c r="A71" t="s">
         <v>115</v>
       </c>
-      <c r="B71">
-        <v>9</v>
+      <c r="B71" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="C71" t="s">
         <v>107</v>
@@ -3125,8 +3699,8 @@
       <c r="A72" t="s">
         <v>115</v>
       </c>
-      <c r="B72">
-        <v>10</v>
+      <c r="B72" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C72" t="s">
         <v>100</v>
@@ -3151,8 +3725,8 @@
       <c r="A73" t="s">
         <v>59</v>
       </c>
-      <c r="B73">
-        <v>0</v>
+      <c r="B73" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="C73" t="s">
         <v>78</v>
@@ -3174,8 +3748,8 @@
       <c r="A74" t="s">
         <v>59</v>
       </c>
-      <c r="B74">
-        <v>1</v>
+      <c r="B74" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="C74" t="s">
         <v>104</v>
@@ -3203,8 +3777,8 @@
       <c r="A75" t="s">
         <v>59</v>
       </c>
-      <c r="B75">
-        <v>2</v>
+      <c r="B75" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="C75" t="s">
         <v>105</v>
@@ -3232,8 +3806,8 @@
       <c r="A76" t="s">
         <v>59</v>
       </c>
-      <c r="B76">
-        <v>3</v>
+      <c r="B76" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="C76" t="s">
         <v>82</v>
@@ -3258,8 +3832,8 @@
       <c r="A77" t="s">
         <v>59</v>
       </c>
-      <c r="B77">
-        <v>4</v>
+      <c r="B77" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="C77" t="s">
         <v>80</v>
@@ -3284,8 +3858,8 @@
       <c r="A78" t="s">
         <v>59</v>
       </c>
-      <c r="B78">
-        <v>5</v>
+      <c r="B78" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="C78" t="s">
         <v>106</v>
@@ -3313,8 +3887,8 @@
       <c r="A79" t="s">
         <v>59</v>
       </c>
-      <c r="B79">
-        <v>6</v>
+      <c r="B79" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="C79" t="s">
         <v>97</v>
@@ -3342,8 +3916,8 @@
       <c r="A80" t="s">
         <v>59</v>
       </c>
-      <c r="B80">
-        <v>7</v>
+      <c r="B80" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="C80" t="s">
         <v>82</v>
@@ -3368,8 +3942,8 @@
       <c r="A81" t="s">
         <v>59</v>
       </c>
-      <c r="B81">
-        <v>8</v>
+      <c r="B81" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="C81" t="s">
         <v>86</v>
@@ -3397,8 +3971,8 @@
       <c r="A82" t="s">
         <v>59</v>
       </c>
-      <c r="B82">
-        <v>9</v>
+      <c r="B82" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="C82" t="s">
         <v>82</v>
@@ -3423,8 +3997,8 @@
       <c r="A83" t="s">
         <v>59</v>
       </c>
-      <c r="B83">
-        <v>10</v>
+      <c r="B83" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="C83" t="s">
         <v>82</v>
@@ -3449,8 +4023,8 @@
       <c r="A84" t="s">
         <v>59</v>
       </c>
-      <c r="B84">
-        <v>11</v>
+      <c r="B84" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="C84" t="s">
         <v>107</v>
@@ -3478,8 +4052,8 @@
       <c r="A85" t="s">
         <v>59</v>
       </c>
-      <c r="B85">
-        <v>12</v>
+      <c r="B85" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="C85" t="s">
         <v>88</v>
@@ -3507,8 +4081,8 @@
       <c r="A86" t="s">
         <v>59</v>
       </c>
-      <c r="B86">
-        <v>13</v>
+      <c r="B86" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="C86" t="s">
         <v>100</v>
@@ -3533,8 +4107,8 @@
       <c r="A87" t="s">
         <v>60</v>
       </c>
-      <c r="B87" s="2">
-        <v>0</v>
+      <c r="B87" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="C87" t="s">
         <v>78</v>
@@ -3556,8 +4130,8 @@
       <c r="A88" t="s">
         <v>60</v>
       </c>
-      <c r="B88" s="2">
-        <v>1</v>
+      <c r="B88" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="C88" t="s">
         <v>96</v>
@@ -3585,8 +4159,8 @@
       <c r="A89" t="s">
         <v>60</v>
       </c>
-      <c r="B89" s="2">
-        <v>2</v>
+      <c r="B89" s="2" t="s">
+        <v>221</v>
       </c>
       <c r="C89" t="s">
         <v>80</v>
@@ -3614,8 +4188,8 @@
       <c r="A90" t="s">
         <v>60</v>
       </c>
-      <c r="B90" s="2">
-        <v>3</v>
+      <c r="B90" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="C90" t="s">
         <v>95</v>
@@ -3643,8 +4217,8 @@
       <c r="A91" t="s">
         <v>60</v>
       </c>
-      <c r="B91" s="2">
-        <v>4</v>
+      <c r="B91" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="C91" t="s">
         <v>97</v>
@@ -3672,8 +4246,8 @@
       <c r="A92" t="s">
         <v>60</v>
       </c>
-      <c r="B92" s="2">
-        <v>5</v>
+      <c r="B92" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="C92" t="s">
         <v>82</v>
@@ -3698,8 +4272,8 @@
       <c r="A93" t="s">
         <v>60</v>
       </c>
-      <c r="B93" s="2">
-        <v>6</v>
+      <c r="B93" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C93" t="s">
         <v>114</v>
@@ -3727,8 +4301,8 @@
       <c r="A94" t="s">
         <v>60</v>
       </c>
-      <c r="B94" s="2">
-        <v>7</v>
+      <c r="B94" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="C94" t="s">
         <v>82</v>
@@ -3753,8 +4327,8 @@
       <c r="A95" t="s">
         <v>60</v>
       </c>
-      <c r="B95" s="2">
-        <v>8</v>
+      <c r="B95" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="C95" t="s">
         <v>82</v>
@@ -3779,8 +4353,8 @@
       <c r="A96" t="s">
         <v>60</v>
       </c>
-      <c r="B96" s="2">
-        <v>9</v>
+      <c r="B96" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="C96" t="s">
         <v>107</v>
@@ -3805,8 +4379,8 @@
       <c r="A97" t="s">
         <v>61</v>
       </c>
-      <c r="B97" s="2">
-        <v>0</v>
+      <c r="B97" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="C97" t="s">
         <v>78</v>
@@ -3828,8 +4402,8 @@
       <c r="A98" t="s">
         <v>61</v>
       </c>
-      <c r="B98" s="2">
-        <v>1</v>
+      <c r="B98" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="C98" t="s">
         <v>104</v>
@@ -3857,8 +4431,8 @@
       <c r="A99" t="s">
         <v>61</v>
       </c>
-      <c r="B99" s="2">
-        <v>2</v>
+      <c r="B99" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="C99" t="s">
         <v>105</v>
@@ -3886,8 +4460,8 @@
       <c r="A100" t="s">
         <v>61</v>
       </c>
-      <c r="B100" s="2">
-        <v>3</v>
+      <c r="B100" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="C100" t="s">
         <v>82</v>
@@ -3912,8 +4486,8 @@
       <c r="A101" t="s">
         <v>61</v>
       </c>
-      <c r="B101" s="2">
-        <v>4</v>
+      <c r="B101" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="C101" t="s">
         <v>80</v>
@@ -3938,8 +4512,8 @@
       <c r="A102" t="s">
         <v>61</v>
       </c>
-      <c r="B102" s="2">
-        <v>5</v>
+      <c r="B102" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="C102" t="s">
         <v>106</v>
@@ -3967,8 +4541,8 @@
       <c r="A103" t="s">
         <v>61</v>
       </c>
-      <c r="B103" s="2">
-        <v>6</v>
+      <c r="B103" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="C103" t="s">
         <v>97</v>
@@ -3996,8 +4570,8 @@
       <c r="A104" t="s">
         <v>61</v>
       </c>
-      <c r="B104" s="2">
-        <v>7</v>
+      <c r="B104" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="C104" t="s">
         <v>82</v>
@@ -4022,8 +4596,8 @@
       <c r="A105" t="s">
         <v>61</v>
       </c>
-      <c r="B105" s="2">
-        <v>8</v>
+      <c r="B105" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="C105" t="s">
         <v>114</v>
@@ -4051,8 +4625,8 @@
       <c r="A106" t="s">
         <v>61</v>
       </c>
-      <c r="B106" s="2">
-        <v>9</v>
+      <c r="B106" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="C106" t="s">
         <v>82</v>
@@ -4077,8 +4651,8 @@
       <c r="A107" t="s">
         <v>61</v>
       </c>
-      <c r="B107" s="2">
-        <v>10</v>
+      <c r="B107" s="2" t="s">
+        <v>237</v>
       </c>
       <c r="C107" t="s">
         <v>82</v>
@@ -4103,8 +4677,8 @@
       <c r="A108" t="s">
         <v>61</v>
       </c>
-      <c r="B108" s="2">
-        <v>11</v>
+      <c r="B108" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="C108" t="s">
         <v>107</v>
@@ -4129,8 +4703,8 @@
       <c r="A109" t="s">
         <v>62</v>
       </c>
-      <c r="B109" s="2">
-        <v>0</v>
+      <c r="B109" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="C109" t="s">
         <v>78</v>
@@ -4152,8 +4726,8 @@
       <c r="A110" t="s">
         <v>62</v>
       </c>
-      <c r="B110" s="2">
-        <v>1</v>
+      <c r="B110" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="C110" t="s">
         <v>96</v>
@@ -4181,8 +4755,8 @@
       <c r="A111" t="s">
         <v>62</v>
       </c>
-      <c r="B111" s="2">
-        <v>2</v>
+      <c r="B111" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="C111" t="s">
         <v>80</v>
@@ -4210,8 +4784,8 @@
       <c r="A112" t="s">
         <v>62</v>
       </c>
-      <c r="B112" s="2">
-        <v>3</v>
+      <c r="B112" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="C112" t="s">
         <v>95</v>
@@ -4239,8 +4813,8 @@
       <c r="A113" t="s">
         <v>62</v>
       </c>
-      <c r="B113" s="2">
-        <v>4</v>
+      <c r="B113" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="C113" t="s">
         <v>97</v>
@@ -4268,8 +4842,8 @@
       <c r="A114" t="s">
         <v>62</v>
       </c>
-      <c r="B114" s="2">
-        <v>5</v>
+      <c r="B114" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="C114" t="s">
         <v>82</v>
@@ -4294,8 +4868,8 @@
       <c r="A115" t="s">
         <v>62</v>
       </c>
-      <c r="B115" s="2">
-        <v>6</v>
+      <c r="B115" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="C115" t="s">
         <v>98</v>
@@ -4323,8 +4897,8 @@
       <c r="A116" t="s">
         <v>62</v>
       </c>
-      <c r="B116" s="2">
-        <v>7</v>
+      <c r="B116" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="C116" t="s">
         <v>82</v>
@@ -4349,8 +4923,8 @@
       <c r="A117" t="s">
         <v>62</v>
       </c>
-      <c r="B117" s="2">
-        <v>8</v>
+      <c r="B117" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="C117" t="s">
         <v>100</v>
@@ -4375,8 +4949,8 @@
       <c r="A118" t="s">
         <v>63</v>
       </c>
-      <c r="B118" s="2">
-        <v>0</v>
+      <c r="B118" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="C118" t="s">
         <v>78</v>
@@ -4398,8 +4972,8 @@
       <c r="A119" t="s">
         <v>63</v>
       </c>
-      <c r="B119" s="2">
-        <v>1</v>
+      <c r="B119" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="C119" t="s">
         <v>104</v>
@@ -4427,8 +5001,8 @@
       <c r="A120" t="s">
         <v>63</v>
       </c>
-      <c r="B120" s="2">
-        <v>2</v>
+      <c r="B120" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="C120" t="s">
         <v>105</v>
@@ -4456,8 +5030,8 @@
       <c r="A121" t="s">
         <v>63</v>
       </c>
-      <c r="B121" s="2">
-        <v>3</v>
+      <c r="B121" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="C121" t="s">
         <v>82</v>
@@ -4482,8 +5056,8 @@
       <c r="A122" t="s">
         <v>63</v>
       </c>
-      <c r="B122" s="2">
-        <v>4</v>
+      <c r="B122" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="C122" t="s">
         <v>80</v>
@@ -4508,8 +5082,8 @@
       <c r="A123" t="s">
         <v>63</v>
       </c>
-      <c r="B123" s="2">
-        <v>5</v>
+      <c r="B123" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="C123" t="s">
         <v>106</v>
@@ -4537,8 +5111,8 @@
       <c r="A124" t="s">
         <v>63</v>
       </c>
-      <c r="B124" s="2">
-        <v>6</v>
+      <c r="B124" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="C124" t="s">
         <v>97</v>
@@ -4566,8 +5140,8 @@
       <c r="A125" t="s">
         <v>63</v>
       </c>
-      <c r="B125" s="2">
-        <v>7</v>
+      <c r="B125" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="C125" t="s">
         <v>82</v>
@@ -4592,8 +5166,8 @@
       <c r="A126" t="s">
         <v>63</v>
       </c>
-      <c r="B126" s="2">
-        <v>8</v>
+      <c r="B126" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="C126" t="s">
         <v>86</v>
@@ -4621,8 +5195,8 @@
       <c r="A127" t="s">
         <v>63</v>
       </c>
-      <c r="B127" s="2">
-        <v>9</v>
+      <c r="B127" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="C127" t="s">
         <v>82</v>
@@ -4647,8 +5221,8 @@
       <c r="A128" t="s">
         <v>63</v>
       </c>
-      <c r="B128" s="2">
-        <v>10</v>
+      <c r="B128" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="C128" t="s">
         <v>82</v>
@@ -4673,8 +5247,8 @@
       <c r="A129" t="s">
         <v>63</v>
       </c>
-      <c r="B129" s="2">
-        <v>11</v>
+      <c r="B129" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="C129" t="s">
         <v>107</v>
@@ -4702,8 +5276,8 @@
       <c r="A130" t="s">
         <v>63</v>
       </c>
-      <c r="B130" s="2">
-        <v>12</v>
+      <c r="B130" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="C130" t="s">
         <v>88</v>
@@ -4731,8 +5305,8 @@
       <c r="A131" t="s">
         <v>63</v>
       </c>
-      <c r="B131" s="2">
-        <v>13</v>
+      <c r="B131" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="C131" t="s">
         <v>100</v>
@@ -4757,8 +5331,8 @@
       <c r="A132" t="s">
         <v>64</v>
       </c>
-      <c r="B132" s="2">
-        <v>0</v>
+      <c r="B132" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="C132" t="s">
         <v>78</v>
@@ -4780,8 +5354,8 @@
       <c r="A133" t="s">
         <v>64</v>
       </c>
-      <c r="B133" s="2">
-        <v>1</v>
+      <c r="B133" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="C133" t="s">
         <v>104</v>
@@ -4809,8 +5383,8 @@
       <c r="A134" t="s">
         <v>64</v>
       </c>
-      <c r="B134" s="2">
-        <v>2</v>
+      <c r="B134" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="C134" t="s">
         <v>105</v>
@@ -4838,8 +5412,8 @@
       <c r="A135" t="s">
         <v>64</v>
       </c>
-      <c r="B135" s="2">
-        <v>3</v>
+      <c r="B135" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="C135" t="s">
         <v>82</v>
@@ -4864,8 +5438,8 @@
       <c r="A136" t="s">
         <v>64</v>
       </c>
-      <c r="B136" s="2">
-        <v>4</v>
+      <c r="B136" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="C136" t="s">
         <v>80</v>
@@ -4890,8 +5464,8 @@
       <c r="A137" t="s">
         <v>64</v>
       </c>
-      <c r="B137" s="2">
-        <v>5</v>
+      <c r="B137" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="C137" t="s">
         <v>106</v>
@@ -4919,8 +5493,8 @@
       <c r="A138" t="s">
         <v>64</v>
       </c>
-      <c r="B138" s="2">
-        <v>6</v>
+      <c r="B138" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="C138" t="s">
         <v>97</v>
@@ -4948,8 +5522,8 @@
       <c r="A139" t="s">
         <v>64</v>
       </c>
-      <c r="B139" s="2">
-        <v>7</v>
+      <c r="B139" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="C139" t="s">
         <v>82</v>
@@ -4974,8 +5548,8 @@
       <c r="A140" t="s">
         <v>64</v>
       </c>
-      <c r="B140" s="2">
-        <v>8</v>
+      <c r="B140" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="C140" t="s">
         <v>114</v>
@@ -5003,8 +5577,8 @@
       <c r="A141" t="s">
         <v>64</v>
       </c>
-      <c r="B141" s="2">
-        <v>9</v>
+      <c r="B141" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="C141" t="s">
         <v>82</v>
@@ -5029,8 +5603,8 @@
       <c r="A142" t="s">
         <v>64</v>
       </c>
-      <c r="B142" s="2">
-        <v>10</v>
+      <c r="B142" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="C142" t="s">
         <v>82</v>
@@ -5055,8 +5629,8 @@
       <c r="A143" t="s">
         <v>64</v>
       </c>
-      <c r="B143" s="2">
-        <v>11</v>
+      <c r="B143" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="C143" t="s">
         <v>107</v>
@@ -5081,12 +5655,2296 @@
       <c r="B144" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0EB66BD-C22E-374C-A8FE-C7F74157E1FC}">
+  <dimension ref="A1:E143"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46" t="s">
+        <v>92</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
+      </c>
+      <c r="C47">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="E49">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="E50">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="E51">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>4</v>
+      </c>
+      <c r="E53">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="E54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>99</v>
+      </c>
+      <c r="E55">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56">
+        <v>2</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="E61">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="E63">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="E65">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>82</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="E67">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>82</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="E70">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="E72">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="E78">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="E80">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="E82">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>4</v>
+      </c>
+      <c r="D85" t="s">
+        <v>90</v>
+      </c>
+      <c r="E85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>95</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86" t="s">
+        <v>90</v>
+      </c>
+      <c r="E86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
+        <v>90</v>
+      </c>
+      <c r="E87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
+        <v>90</v>
+      </c>
+      <c r="E88">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="s">
+        <v>90</v>
+      </c>
+      <c r="E89">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90" t="s">
+        <v>90</v>
+      </c>
+      <c r="E90">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>106</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91" t="s">
+        <v>111</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>106</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="s">
+        <v>111</v>
+      </c>
+      <c r="E92">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>106</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>106</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>106</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
+        <v>111</v>
+      </c>
+      <c r="E95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96" t="s">
+        <v>108</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97" t="s">
+        <v>101</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="s">
+        <v>108</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>101</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100" t="s">
+        <v>108</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>96</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101" t="s">
+        <v>101</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>96</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102" t="s">
+        <v>101</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>96</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103" t="s">
+        <v>101</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>96</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="s">
+        <v>101</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>85</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+      <c r="C105">
+        <v>4</v>
+      </c>
+      <c r="D105" t="s">
+        <v>85</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>85</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>4</v>
+      </c>
+      <c r="D106" t="s">
+        <v>85</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>97</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
+        <v>2</v>
+      </c>
+      <c r="D107" t="s">
+        <v>85</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>97</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108">
+        <v>3</v>
+      </c>
+      <c r="D108" t="s">
+        <v>85</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>97</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <v>2</v>
+      </c>
+      <c r="D109" t="s">
+        <v>85</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>97</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110">
+        <v>3</v>
+      </c>
+      <c r="D110" t="s">
+        <v>85</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>97</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111" t="s">
+        <v>85</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>97</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112">
+        <v>3</v>
+      </c>
+      <c r="D112" t="s">
+        <v>85</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>97</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
+        <v>2</v>
+      </c>
+      <c r="D113" t="s">
+        <v>85</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>97</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+      <c r="C114">
+        <v>3</v>
+      </c>
+      <c r="D114" t="s">
+        <v>85</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>97</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
+      <c r="D115" t="s">
+        <v>85</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>105</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+      <c r="C116">
+        <v>2</v>
+      </c>
+      <c r="D116" t="s">
+        <v>109</v>
+      </c>
+      <c r="E116">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>105</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117" t="s">
+        <v>109</v>
+      </c>
+      <c r="E117">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>105</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
+        <v>117</v>
+      </c>
+      <c r="E118">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>105</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119" t="s">
+        <v>109</v>
+      </c>
+      <c r="E119">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>105</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120" t="s">
+        <v>117</v>
+      </c>
+      <c r="E120">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>98</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
+        <v>92</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>98</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+      <c r="D122" t="s">
+        <v>92</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>99</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>100</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+      <c r="D124" t="s">
+        <v>103</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>100</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125" t="s">
+        <v>113</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>100</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>2</v>
+      </c>
+      <c r="D126" t="s">
+        <v>113</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>100</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127" t="s">
+        <v>103</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>100</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>2</v>
+      </c>
+      <c r="D128" t="s">
+        <v>113</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>107</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>3</v>
+      </c>
+      <c r="D129" t="s">
+        <v>113</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>107</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>2</v>
+      </c>
+      <c r="D130" t="s">
+        <v>113</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>107</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131" t="s">
+        <v>103</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>107</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132" t="s">
+        <v>113</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>107</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="D133" t="s">
+        <v>103</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>107</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>2</v>
+      </c>
+      <c r="D134" t="s">
+        <v>113</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>107</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>2</v>
+      </c>
+      <c r="D135" t="s">
+        <v>113</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>107</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+      <c r="D136" t="s">
+        <v>113</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>88</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>3</v>
+      </c>
+      <c r="D137" t="s">
+        <v>93</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>88</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>3</v>
+      </c>
+      <c r="D138" t="s">
+        <v>93</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>88</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>3</v>
+      </c>
+      <c r="D139" t="s">
+        <v>113</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>88</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>2</v>
+      </c>
+      <c r="D140" t="s">
+        <v>113</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>88</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+      <c r="D141" t="s">
+        <v>113</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>87</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>4</v>
+      </c>
+      <c r="D142" t="s">
+        <v>93</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>87</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>4</v>
+      </c>
+      <c r="D143" t="s">
+        <v>93</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E144">
+    <sortCondition ref="A2:A144"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12FB3095-0DE8-7946-9F31-F607C18FE7AD}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5131,7 +7989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF55ADFD-5293-584D-80F6-F72E0325B131}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5151,7 +8009,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC921586-67AE-EB42-A780-816989418384}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5187,7 +8045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66B1D5C-CC71-A540-A7B7-41DA96CE5644}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5232,7 +8090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28067E6D-F6AB-0B46-8A48-AE14A0528440}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5274,7 +8132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4B85EED-8CB1-1848-A79F-4A3D9164D609}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5376,58 +8234,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53EB7CAF-F72D-D848-9389-E9B506E330DC}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/ontology/v2.01/cellfie_import.xlsx
+++ b/ontology/v2.01/cellfie_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurasla/Documents/GitHub/bedreflyt/ontology/v2.01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA80A41-341A-CE44-BADC-D62C22D9B3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4B1CE6-09FB-0C4D-B754-16E816B9F624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="1220" windowWidth="61860" windowHeight="24360" activeTab="1" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
+    <workbookView xWindow="16060" yWindow="500" windowWidth="45800" windowHeight="25280" activeTab="1" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
   </bookViews>
   <sheets>
     <sheet name="TreatmentJourneys" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="270">
   <si>
     <t>DIAGNOSIS</t>
   </si>
@@ -845,6 +845,15 @@
   </si>
   <si>
     <t>C71.3_Standard_STEP_10</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>NEXT</t>
+  </si>
+  <si>
+    <t>PREVIOUS</t>
   </si>
 </sst>
 </file>
@@ -1731,20 +1740,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{272AE597-DF5B-6144-9B2B-E3571D9F6B3C}">
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:K144"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" customWidth="1"/>
     <col min="2" max="2" width="35.1640625" customWidth="1"/>
-    <col min="3" max="5" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24.5" customWidth="1"/>
+    <col min="6" max="7" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1755,25 +1766,31 @@
         <v>38</v>
       </c>
       <c r="D1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>94</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>77</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -1784,19 +1801,22 @@
         <v>78</v>
       </c>
       <c r="D2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
+      <c r="H2" t="s">
+        <v>267</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1807,25 +1827,31 @@
         <v>79</v>
       </c>
       <c r="D3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" t="s">
         <v>80</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>78</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
+      <c r="H3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I3">
         <v>4</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>89</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -1836,22 +1862,28 @@
         <v>80</v>
       </c>
       <c r="D4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" t="s">
         <v>81</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>79</v>
       </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4">
         <v>4</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -1862,25 +1894,31 @@
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" t="s">
         <v>80</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5">
         <v>4</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>90</v>
       </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -1891,22 +1929,28 @@
         <v>82</v>
       </c>
       <c r="D6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F6" t="s">
         <v>83</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>81</v>
       </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -1917,25 +1961,31 @@
         <v>83</v>
       </c>
       <c r="D7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" t="s">
         <v>84</v>
       </c>
-      <c r="E7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
+      <c r="G7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" t="s">
+        <v>267</v>
+      </c>
+      <c r="I7">
         <v>4</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>91</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -1946,25 +1996,31 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F8" t="s">
         <v>85</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>83</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>267</v>
       </c>
       <c r="I8">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -1975,25 +2031,31 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" t="s">
         <v>84</v>
       </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
+      <c r="H9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9">
         <v>4</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>85</v>
       </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -2004,22 +2066,28 @@
         <v>82</v>
       </c>
       <c r="D10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" t="s">
         <v>86</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>85</v>
       </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10">
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10">
         <v>4</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -2030,25 +2098,31 @@
         <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
+        <v>154</v>
+      </c>
+      <c r="F11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" t="s">
+        <v>267</v>
+      </c>
+      <c r="I11">
         <v>4</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>92</v>
       </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -2059,22 +2133,28 @@
         <v>82</v>
       </c>
       <c r="D12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" t="s">
         <v>86</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>86</v>
       </c>
-      <c r="F12">
-        <v>3</v>
-      </c>
-      <c r="G12">
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
         <v>4</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -2085,25 +2165,31 @@
         <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
+        <v>156</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" t="s">
+        <v>267</v>
+      </c>
+      <c r="I13">
         <v>4</v>
       </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
         <v>92</v>
       </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -2114,22 +2200,28 @@
         <v>82</v>
       </c>
       <c r="D14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14" t="s">
         <v>87</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>86</v>
       </c>
-      <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="G14">
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14">
         <v>4</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -2140,25 +2232,31 @@
         <v>87</v>
       </c>
       <c r="D15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" t="s">
         <v>88</v>
       </c>
-      <c r="E15" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
+      <c r="G15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s">
+        <v>267</v>
+      </c>
+      <c r="I15">
         <v>4</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>93</v>
       </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -2169,22 +2267,25 @@
         <v>88</v>
       </c>
       <c r="E16" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" t="s">
         <v>87</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
+      <c r="H16" t="s">
+        <v>267</v>
+      </c>
+      <c r="I16">
         <v>3</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>93</v>
       </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -2195,19 +2296,22 @@
         <v>78</v>
       </c>
       <c r="D17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" t="s">
         <v>79</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
+      <c r="H17" t="s">
+        <v>267</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -2218,25 +2322,31 @@
         <v>79</v>
       </c>
       <c r="D18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" t="s">
         <v>80</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>78</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
+      <c r="H18" t="s">
+        <v>267</v>
+      </c>
+      <c r="I18">
         <v>4</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>89</v>
       </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -2247,22 +2357,28 @@
         <v>80</v>
       </c>
       <c r="D19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F19" t="s">
         <v>81</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>79</v>
       </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="G19">
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19">
         <v>4</v>
       </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -2273,25 +2389,31 @@
         <v>81</v>
       </c>
       <c r="D20" t="s">
+        <v>163</v>
+      </c>
+      <c r="E20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20" t="s">
         <v>95</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>80</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
+      <c r="H20" t="s">
+        <v>267</v>
+      </c>
+      <c r="I20">
         <v>4</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" t="s">
         <v>90</v>
       </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -2302,25 +2424,31 @@
         <v>95</v>
       </c>
       <c r="D21" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F21" t="s">
         <v>85</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>81</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
+      <c r="H21" t="s">
+        <v>267</v>
+      </c>
+      <c r="I21">
         <v>4</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>90</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -2331,25 +2459,31 @@
         <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="E22" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" t="s">
         <v>95</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
+      <c r="H22" t="s">
+        <v>267</v>
+      </c>
+      <c r="I22">
         <v>4</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>85</v>
       </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -2360,22 +2494,28 @@
         <v>82</v>
       </c>
       <c r="D23" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" t="s">
         <v>86</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>85</v>
       </c>
-      <c r="F23">
-        <v>3</v>
-      </c>
-      <c r="G23">
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23">
         <v>4</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2386,25 +2526,31 @@
         <v>86</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
+        <v>165</v>
+      </c>
+      <c r="F24" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" t="s">
+        <v>267</v>
+      </c>
+      <c r="I24">
         <v>4</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" t="s">
         <v>92</v>
       </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -2415,22 +2561,28 @@
         <v>82</v>
       </c>
       <c r="D25" t="s">
+        <v>168</v>
+      </c>
+      <c r="E25" t="s">
+        <v>166</v>
+      </c>
+      <c r="F25" t="s">
         <v>86</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>86</v>
       </c>
-      <c r="F25">
-        <v>3</v>
-      </c>
-      <c r="G25">
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
         <v>4</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -2441,25 +2593,31 @@
         <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
+        <v>167</v>
+      </c>
+      <c r="F26" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" t="s">
+        <v>267</v>
+      </c>
+      <c r="I26">
         <v>4</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
         <v>92</v>
       </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -2470,22 +2628,28 @@
         <v>82</v>
       </c>
       <c r="D27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" t="s">
         <v>87</v>
       </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>86</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
+      <c r="H27" t="s">
+        <v>267</v>
+      </c>
+      <c r="I27">
         <v>4</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -2496,25 +2660,31 @@
         <v>87</v>
       </c>
       <c r="D28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28" t="s">
         <v>88</v>
       </c>
-      <c r="E28" t="s">
-        <v>82</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
+      <c r="G28" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" t="s">
+        <v>267</v>
+      </c>
+      <c r="I28">
         <v>4</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
         <v>93</v>
       </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -2525,22 +2695,25 @@
         <v>88</v>
       </c>
       <c r="E29" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" t="s">
         <v>87</v>
       </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
+      <c r="H29" t="s">
+        <v>267</v>
+      </c>
+      <c r="I29">
         <v>3</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
         <v>93</v>
       </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -2551,19 +2724,22 @@
         <v>78</v>
       </c>
       <c r="D30" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" t="s">
         <v>96</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
+      <c r="H30" t="s">
+        <v>267</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>55</v>
       </c>
@@ -2574,25 +2750,31 @@
         <v>96</v>
       </c>
       <c r="D31" t="s">
+        <v>172</v>
+      </c>
+      <c r="E31" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" t="s">
         <v>80</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>78</v>
       </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
       <c r="H31" t="s">
+        <v>267</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
         <v>101</v>
       </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>55</v>
       </c>
@@ -2603,25 +2785,31 @@
         <v>80</v>
       </c>
       <c r="D32" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" t="s">
+        <v>171</v>
+      </c>
+      <c r="F32" t="s">
         <v>80</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>96</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
       <c r="H32" t="s">
+        <v>267</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s">
         <v>102</v>
       </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -2632,22 +2820,28 @@
         <v>80</v>
       </c>
       <c r="D33" t="s">
+        <v>174</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" t="s">
         <v>95</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>80</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
+      <c r="H33" t="s">
+        <v>33</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -2658,25 +2852,31 @@
         <v>95</v>
       </c>
       <c r="D34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E34" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" t="s">
         <v>97</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>80</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
       <c r="H34" t="s">
+        <v>267</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34" t="s">
         <v>90</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -2687,25 +2887,31 @@
         <v>97</v>
       </c>
       <c r="D35" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="E35" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" t="s">
         <v>95</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>2</v>
-      </c>
       <c r="H35" t="s">
+        <v>267</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35" t="s">
         <v>85</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -2716,22 +2922,28 @@
         <v>82</v>
       </c>
       <c r="D36" t="s">
+        <v>177</v>
+      </c>
+      <c r="E36" t="s">
+        <v>175</v>
+      </c>
+      <c r="F36" t="s">
         <v>98</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>97</v>
       </c>
-      <c r="F36">
-        <v>2</v>
-      </c>
-      <c r="G36">
-        <v>2</v>
+      <c r="H36" t="s">
+        <v>34</v>
       </c>
       <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="K36">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>55</v>
       </c>
@@ -2742,25 +2954,31 @@
         <v>98</v>
       </c>
       <c r="D37" t="s">
+        <v>178</v>
+      </c>
+      <c r="E37" t="s">
+        <v>176</v>
+      </c>
+      <c r="F37" t="s">
         <v>99</v>
       </c>
-      <c r="E37" t="s">
-        <v>82</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
+      <c r="G37" t="s">
+        <v>82</v>
       </c>
       <c r="H37" t="s">
+        <v>267</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37" t="s">
         <v>92</v>
       </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -2771,22 +2989,28 @@
         <v>99</v>
       </c>
       <c r="D38" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" t="s">
+        <v>177</v>
+      </c>
+      <c r="F38" t="s">
         <v>100</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>98</v>
       </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
+      <c r="H38" t="s">
+        <v>33</v>
       </c>
       <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="K38">
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>55</v>
       </c>
@@ -2797,22 +3021,25 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>178</v>
+      </c>
+      <c r="G39" t="s">
         <v>99</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
       <c r="H39" t="s">
+        <v>267</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39" t="s">
         <v>103</v>
       </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>56</v>
       </c>
@@ -2823,19 +3050,22 @@
         <v>78</v>
       </c>
       <c r="D40" t="s">
+        <v>179</v>
+      </c>
+      <c r="F40" t="s">
         <v>104</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
+      <c r="H40" t="s">
+        <v>267</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>56</v>
       </c>
@@ -2846,25 +3076,31 @@
         <v>104</v>
       </c>
       <c r="D41" t="s">
+        <v>180</v>
+      </c>
+      <c r="E41" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" t="s">
         <v>105</v>
       </c>
-      <c r="E41" t="s">
+      <c r="G41" t="s">
         <v>78</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>2</v>
-      </c>
       <c r="H41" t="s">
+        <v>267</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41" t="s">
         <v>108</v>
       </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -2875,25 +3111,31 @@
         <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="E42" t="s">
+        <v>179</v>
+      </c>
+      <c r="F42" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" t="s">
         <v>104</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>2</v>
-      </c>
       <c r="H42" t="s">
+        <v>267</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42" t="s">
         <v>109</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -2904,25 +3146,31 @@
         <v>82</v>
       </c>
       <c r="D43" t="s">
+        <v>182</v>
+      </c>
+      <c r="E43" t="s">
+        <v>180</v>
+      </c>
+      <c r="F43" t="s">
         <v>80</v>
       </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>105</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43">
-        <v>2</v>
-      </c>
       <c r="H43" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43" t="s">
         <v>99</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -2933,25 +3181,31 @@
         <v>80</v>
       </c>
       <c r="D44" t="s">
+        <v>183</v>
+      </c>
+      <c r="E44" t="s">
+        <v>181</v>
+      </c>
+      <c r="F44" t="s">
         <v>106</v>
       </c>
-      <c r="E44" t="s">
-        <v>82</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44">
-        <v>2</v>
+      <c r="G44" t="s">
+        <v>82</v>
       </c>
       <c r="H44" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="J44" t="s">
         <v>110</v>
       </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -2962,25 +3216,31 @@
         <v>106</v>
       </c>
       <c r="D45" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" t="s">
+        <v>182</v>
+      </c>
+      <c r="F45" t="s">
         <v>97</v>
       </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
         <v>80</v>
       </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>2</v>
-      </c>
       <c r="H45" t="s">
+        <v>267</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="J45" t="s">
         <v>111</v>
       </c>
-      <c r="I45">
+      <c r="K45">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -2991,25 +3251,31 @@
         <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="E46" t="s">
+        <v>183</v>
+      </c>
+      <c r="F46" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" t="s">
         <v>106</v>
       </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
+      <c r="H46" t="s">
+        <v>267</v>
+      </c>
+      <c r="I46">
         <v>3</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" t="s">
         <v>85</v>
       </c>
-      <c r="I46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -3020,25 +3286,31 @@
         <v>82</v>
       </c>
       <c r="D47" t="s">
+        <v>186</v>
+      </c>
+      <c r="E47" t="s">
+        <v>184</v>
+      </c>
+      <c r="F47" t="s">
         <v>86</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>97</v>
       </c>
-      <c r="F47">
-        <v>2</v>
-      </c>
-      <c r="G47">
+      <c r="H47" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47">
         <v>3</v>
       </c>
-      <c r="H47" t="s">
+      <c r="J47" t="s">
         <v>112</v>
       </c>
-      <c r="I47">
+      <c r="K47">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3049,25 +3321,31 @@
         <v>86</v>
       </c>
       <c r="D48" t="s">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="E48" t="s">
-        <v>82</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
+        <v>185</v>
+      </c>
+      <c r="F48" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" t="s">
+        <v>82</v>
+      </c>
+      <c r="H48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I48">
         <v>3</v>
       </c>
-      <c r="H48" t="s">
+      <c r="J48" t="s">
         <v>92</v>
       </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -3078,25 +3356,31 @@
         <v>82</v>
       </c>
       <c r="D49" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="E49" t="s">
+        <v>186</v>
+      </c>
+      <c r="F49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" t="s">
         <v>86</v>
       </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
-      <c r="G49">
+      <c r="H49" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49">
         <v>3</v>
       </c>
-      <c r="H49" t="s">
+      <c r="J49" t="s">
         <v>9</v>
       </c>
-      <c r="I49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -3107,25 +3391,31 @@
         <v>82</v>
       </c>
       <c r="D50" t="s">
+        <v>189</v>
+      </c>
+      <c r="E50" t="s">
+        <v>187</v>
+      </c>
+      <c r="F50" t="s">
         <v>107</v>
       </c>
-      <c r="E50" t="s">
-        <v>82</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50">
+      <c r="G50" t="s">
+        <v>82</v>
+      </c>
+      <c r="H50" t="s">
+        <v>33</v>
+      </c>
+      <c r="I50">
         <v>3</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>8</v>
       </c>
-      <c r="I50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -3136,25 +3426,31 @@
         <v>107</v>
       </c>
       <c r="D51" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" t="s">
         <v>88</v>
       </c>
-      <c r="E51" t="s">
-        <v>82</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51">
+      <c r="G51" t="s">
+        <v>82</v>
+      </c>
+      <c r="H51" t="s">
+        <v>267</v>
+      </c>
+      <c r="I51">
         <v>3</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>113</v>
       </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -3165,22 +3461,25 @@
         <v>88</v>
       </c>
       <c r="E52" t="s">
+        <v>189</v>
+      </c>
+      <c r="G52" t="s">
         <v>107</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
+      <c r="H52" t="s">
+        <v>267</v>
+      </c>
+      <c r="I52">
         <v>3</v>
       </c>
-      <c r="H52" t="s">
+      <c r="J52" t="s">
         <v>113</v>
       </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -3190,20 +3489,23 @@
       <c r="C53" t="s">
         <v>78</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F53" t="s">
         <v>79</v>
       </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
+      <c r="H53" t="s">
+        <v>267</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -3213,26 +3515,32 @@
       <c r="C54" t="s">
         <v>79</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F54" t="s">
         <v>80</v>
       </c>
-      <c r="E54" t="s">
+      <c r="G54" t="s">
         <v>78</v>
       </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>2</v>
-      </c>
       <c r="H54" t="s">
+        <v>267</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+      <c r="J54" t="s">
         <v>89</v>
       </c>
-      <c r="I54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -3242,23 +3550,29 @@
       <c r="C55" t="s">
         <v>80</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F55" t="s">
         <v>80</v>
       </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>79</v>
       </c>
-      <c r="F55">
-        <v>2</v>
-      </c>
-      <c r="G55">
-        <v>2</v>
+      <c r="H55" t="s">
+        <v>34</v>
       </c>
       <c r="I55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -3268,23 +3582,29 @@
       <c r="C56" t="s">
         <v>80</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F56" t="s">
         <v>95</v>
       </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
         <v>80</v>
       </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56">
-        <v>2</v>
+      <c r="H56" t="s">
+        <v>33</v>
       </c>
       <c r="I56">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>57</v>
       </c>
@@ -3294,26 +3614,32 @@
       <c r="C57" t="s">
         <v>95</v>
       </c>
-      <c r="D57" t="s">
-        <v>82</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="D57" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F57" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s">
         <v>80</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>3</v>
-      </c>
       <c r="H57" t="s">
-        <v>90</v>
+        <v>267</v>
       </c>
       <c r="I57">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J57" t="s">
+        <v>90</v>
+      </c>
+      <c r="K57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -3323,23 +3649,29 @@
       <c r="C58" t="s">
         <v>82</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F58" t="s">
         <v>86</v>
       </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>95</v>
       </c>
-      <c r="F58">
-        <v>2</v>
-      </c>
-      <c r="G58">
+      <c r="H58" t="s">
+        <v>34</v>
+      </c>
+      <c r="I58">
         <v>3</v>
       </c>
-      <c r="I58">
+      <c r="K58">
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -3349,26 +3681,32 @@
       <c r="C59" t="s">
         <v>86</v>
       </c>
-      <c r="D59" t="s">
-        <v>82</v>
-      </c>
-      <c r="E59" t="s">
-        <v>82</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
+      <c r="D59" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F59" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" t="s">
+        <v>82</v>
+      </c>
+      <c r="H59" t="s">
+        <v>267</v>
+      </c>
+      <c r="I59">
         <v>3</v>
       </c>
-      <c r="H59" t="s">
+      <c r="J59" t="s">
         <v>92</v>
       </c>
-      <c r="I59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>57</v>
       </c>
@@ -3378,23 +3716,29 @@
       <c r="C60" t="s">
         <v>82</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F60" t="s">
         <v>107</v>
       </c>
-      <c r="E60" t="s">
+      <c r="G60" t="s">
         <v>86</v>
       </c>
-      <c r="F60">
-        <v>2</v>
-      </c>
-      <c r="G60">
+      <c r="H60" t="s">
+        <v>34</v>
+      </c>
+      <c r="I60">
         <v>3</v>
       </c>
-      <c r="I60">
+      <c r="K60">
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>57</v>
       </c>
@@ -3404,23 +3748,26 @@
       <c r="C61" t="s">
         <v>107</v>
       </c>
-      <c r="E61" t="s">
-        <v>82</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>2</v>
+      <c r="E61" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G61" t="s">
+        <v>82</v>
       </c>
       <c r="H61" t="s">
+        <v>267</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61" t="s">
         <v>113</v>
       </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -3430,20 +3777,23 @@
       <c r="C62" t="s">
         <v>78</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F62" t="s">
         <v>96</v>
       </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
+      <c r="H62" t="s">
+        <v>267</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>115</v>
       </c>
@@ -3453,26 +3803,32 @@
       <c r="C63" t="s">
         <v>96</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F63" t="s">
         <v>80</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>78</v>
       </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-      <c r="G63">
-        <v>1</v>
-      </c>
       <c r="H63" t="s">
+        <v>267</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
         <v>101</v>
       </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>115</v>
       </c>
@@ -3482,26 +3838,32 @@
       <c r="C64" t="s">
         <v>80</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F64" t="s">
         <v>95</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>96</v>
       </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
       <c r="H64" t="s">
+        <v>267</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
         <v>116</v>
       </c>
-      <c r="I64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>115</v>
       </c>
@@ -3511,26 +3873,32 @@
       <c r="C65" t="s">
         <v>95</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F65" t="s">
         <v>97</v>
       </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>80</v>
       </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <v>1</v>
-      </c>
       <c r="H65" t="s">
+        <v>267</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65" t="s">
         <v>90</v>
       </c>
-      <c r="I65">
+      <c r="K65">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>115</v>
       </c>
@@ -3540,26 +3908,32 @@
       <c r="C66" t="s">
         <v>97</v>
       </c>
-      <c r="D66" t="s">
-        <v>82</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="D66" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F66" t="s">
+        <v>82</v>
+      </c>
+      <c r="G66" t="s">
         <v>95</v>
       </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66">
-        <v>2</v>
-      </c>
       <c r="H66" t="s">
+        <v>267</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
+      </c>
+      <c r="J66" t="s">
         <v>85</v>
       </c>
-      <c r="I66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>115</v>
       </c>
@@ -3569,23 +3943,29 @@
       <c r="C67" t="s">
         <v>82</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F67" t="s">
         <v>114</v>
       </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>97</v>
       </c>
-      <c r="F67">
-        <v>2</v>
-      </c>
-      <c r="G67">
-        <v>2</v>
+      <c r="H67" t="s">
+        <v>34</v>
       </c>
       <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="K67">
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>115</v>
       </c>
@@ -3595,26 +3975,32 @@
       <c r="C68" t="s">
         <v>114</v>
       </c>
-      <c r="D68" t="s">
-        <v>82</v>
-      </c>
-      <c r="E68" t="s">
-        <v>82</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68">
-        <v>2</v>
+      <c r="D68" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F68" t="s">
+        <v>82</v>
+      </c>
+      <c r="G68" t="s">
+        <v>82</v>
       </c>
       <c r="H68" t="s">
+        <v>267</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+      <c r="J68" t="s">
         <v>92</v>
       </c>
-      <c r="I68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>115</v>
       </c>
@@ -3624,23 +4010,29 @@
       <c r="C69" t="s">
         <v>82</v>
       </c>
-      <c r="D69" t="s">
-        <v>82</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="D69" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F69" t="s">
+        <v>82</v>
+      </c>
+      <c r="G69" t="s">
         <v>114</v>
       </c>
-      <c r="F69">
-        <v>2</v>
-      </c>
-      <c r="G69">
-        <v>2</v>
+      <c r="H69" t="s">
+        <v>34</v>
       </c>
       <c r="I69">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>115</v>
       </c>
@@ -3650,23 +4042,29 @@
       <c r="C70" t="s">
         <v>82</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F70" t="s">
         <v>107</v>
       </c>
-      <c r="E70" t="s">
-        <v>82</v>
-      </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
-      <c r="G70">
-        <v>2</v>
+      <c r="G70" t="s">
+        <v>82</v>
+      </c>
+      <c r="H70" t="s">
+        <v>33</v>
       </c>
       <c r="I70">
+        <v>2</v>
+      </c>
+      <c r="K70">
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>115</v>
       </c>
@@ -3676,26 +4074,32 @@
       <c r="C71" t="s">
         <v>107</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F71" t="s">
         <v>100</v>
       </c>
-      <c r="E71" t="s">
-        <v>82</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71">
-        <v>1</v>
+      <c r="G71" t="s">
+        <v>82</v>
       </c>
       <c r="H71" t="s">
+        <v>267</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71" t="s">
         <v>103</v>
       </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>115</v>
       </c>
@@ -3705,23 +4109,26 @@
       <c r="C72" t="s">
         <v>100</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G72" t="s">
         <v>107</v>
       </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
       <c r="H72" t="s">
+        <v>267</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72" t="s">
         <v>113</v>
       </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>59</v>
       </c>
@@ -3731,20 +4138,23 @@
       <c r="C73" t="s">
         <v>78</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F73" t="s">
         <v>104</v>
       </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73">
-        <v>0</v>
+      <c r="H73" t="s">
+        <v>267</v>
       </c>
       <c r="I73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>59</v>
       </c>
@@ -3754,26 +4164,32 @@
       <c r="C74" t="s">
         <v>104</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F74" t="s">
         <v>105</v>
       </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>78</v>
       </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <v>1</v>
-      </c>
       <c r="H74" t="s">
+        <v>267</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74" t="s">
         <v>101</v>
       </c>
-      <c r="I74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>59</v>
       </c>
@@ -3783,26 +4199,32 @@
       <c r="C75" t="s">
         <v>105</v>
       </c>
-      <c r="D75" t="s">
-        <v>82</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="D75" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F75" t="s">
+        <v>82</v>
+      </c>
+      <c r="G75" t="s">
         <v>104</v>
       </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
       <c r="H75" t="s">
+        <v>267</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75" t="s">
         <v>109</v>
       </c>
-      <c r="I75">
+      <c r="K75">
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>59</v>
       </c>
@@ -3812,23 +4234,29 @@
       <c r="C76" t="s">
         <v>82</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F76" t="s">
         <v>80</v>
       </c>
-      <c r="E76" t="s">
+      <c r="G76" t="s">
         <v>105</v>
       </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76">
-        <v>1</v>
+      <c r="H76" t="s">
+        <v>33</v>
       </c>
       <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="K76">
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>59</v>
       </c>
@@ -3838,23 +4266,29 @@
       <c r="C77" t="s">
         <v>80</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F77" t="s">
         <v>106</v>
       </c>
-      <c r="E77" t="s">
-        <v>82</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-      <c r="G77">
-        <v>1</v>
+      <c r="G77" t="s">
+        <v>82</v>
+      </c>
+      <c r="H77" t="s">
+        <v>33</v>
       </c>
       <c r="I77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>59</v>
       </c>
@@ -3864,26 +4298,32 @@
       <c r="C78" t="s">
         <v>106</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F78" t="s">
         <v>97</v>
       </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>80</v>
       </c>
-      <c r="F78">
-        <v>0</v>
-      </c>
-      <c r="G78">
-        <v>1</v>
-      </c>
       <c r="H78" t="s">
+        <v>267</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78" t="s">
         <v>111</v>
       </c>
-      <c r="I78">
+      <c r="K78">
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>59</v>
       </c>
@@ -3893,26 +4333,32 @@
       <c r="C79" t="s">
         <v>97</v>
       </c>
-      <c r="D79" t="s">
-        <v>82</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="D79" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F79" t="s">
+        <v>82</v>
+      </c>
+      <c r="G79" t="s">
         <v>106</v>
       </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-      <c r="G79">
+      <c r="H79" t="s">
+        <v>267</v>
+      </c>
+      <c r="I79">
         <v>3</v>
       </c>
-      <c r="H79" t="s">
+      <c r="J79" t="s">
         <v>85</v>
       </c>
-      <c r="I79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>59</v>
       </c>
@@ -3922,23 +4368,29 @@
       <c r="C80" t="s">
         <v>82</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F80" t="s">
         <v>86</v>
       </c>
-      <c r="E80" t="s">
+      <c r="G80" t="s">
         <v>97</v>
       </c>
-      <c r="F80">
-        <v>2</v>
-      </c>
-      <c r="G80">
+      <c r="H80" t="s">
+        <v>34</v>
+      </c>
+      <c r="I80">
         <v>3</v>
       </c>
-      <c r="I80">
+      <c r="K80">
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>59</v>
       </c>
@@ -3948,26 +4400,32 @@
       <c r="C81" t="s">
         <v>86</v>
       </c>
-      <c r="D81" t="s">
-        <v>82</v>
-      </c>
-      <c r="E81" t="s">
-        <v>82</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-      <c r="G81">
+      <c r="D81" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F81" t="s">
+        <v>82</v>
+      </c>
+      <c r="G81" t="s">
+        <v>82</v>
+      </c>
+      <c r="H81" t="s">
+        <v>267</v>
+      </c>
+      <c r="I81">
         <v>3</v>
       </c>
-      <c r="H81" t="s">
+      <c r="J81" t="s">
         <v>92</v>
       </c>
-      <c r="I81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>59</v>
       </c>
@@ -3977,23 +4435,29 @@
       <c r="C82" t="s">
         <v>82</v>
       </c>
-      <c r="D82" t="s">
-        <v>82</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="D82" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F82" t="s">
+        <v>82</v>
+      </c>
+      <c r="G82" t="s">
         <v>86</v>
       </c>
-      <c r="F82">
-        <v>2</v>
-      </c>
-      <c r="G82">
+      <c r="H82" t="s">
+        <v>34</v>
+      </c>
+      <c r="I82">
         <v>3</v>
       </c>
-      <c r="I82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>59</v>
       </c>
@@ -4003,23 +4467,29 @@
       <c r="C83" t="s">
         <v>82</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F83" t="s">
         <v>107</v>
       </c>
-      <c r="E83" t="s">
-        <v>82</v>
-      </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-      <c r="G83">
-        <v>2</v>
+      <c r="G83" t="s">
+        <v>82</v>
+      </c>
+      <c r="H83" t="s">
+        <v>33</v>
       </c>
       <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="K83">
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>59</v>
       </c>
@@ -4029,26 +4499,32 @@
       <c r="C84" t="s">
         <v>107</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F84" t="s">
         <v>88</v>
       </c>
-      <c r="E84" t="s">
-        <v>82</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-      <c r="G84">
-        <v>2</v>
+      <c r="G84" t="s">
+        <v>82</v>
       </c>
       <c r="H84" t="s">
+        <v>267</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84" t="s">
         <v>113</v>
       </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>59</v>
       </c>
@@ -4058,26 +4534,32 @@
       <c r="C85" t="s">
         <v>88</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F85" t="s">
         <v>100</v>
       </c>
-      <c r="E85" t="s">
+      <c r="G85" t="s">
         <v>107</v>
       </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-      <c r="G85">
-        <v>2</v>
-      </c>
       <c r="H85" t="s">
+        <v>267</v>
+      </c>
+      <c r="I85">
+        <v>2</v>
+      </c>
+      <c r="J85" t="s">
         <v>113</v>
       </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>59</v>
       </c>
@@ -4087,23 +4569,26 @@
       <c r="C86" t="s">
         <v>100</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G86" t="s">
         <v>88</v>
       </c>
-      <c r="F86">
-        <v>0</v>
-      </c>
-      <c r="G86">
-        <v>2</v>
-      </c>
       <c r="H86" t="s">
+        <v>267</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="J86" t="s">
         <v>113</v>
       </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>60</v>
       </c>
@@ -4113,20 +4598,23 @@
       <c r="C87" t="s">
         <v>78</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F87" t="s">
         <v>96</v>
       </c>
-      <c r="F87">
-        <v>0</v>
-      </c>
-      <c r="G87">
-        <v>0</v>
+      <c r="H87" t="s">
+        <v>267</v>
       </c>
       <c r="I87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>60</v>
       </c>
@@ -4136,26 +4624,32 @@
       <c r="C88" t="s">
         <v>96</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F88" t="s">
         <v>80</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>78</v>
       </c>
-      <c r="F88">
-        <v>0</v>
-      </c>
-      <c r="G88">
-        <v>1</v>
-      </c>
       <c r="H88" t="s">
+        <v>267</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88" t="s">
         <v>101</v>
       </c>
-      <c r="I88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>60</v>
       </c>
@@ -4165,26 +4659,32 @@
       <c r="C89" t="s">
         <v>80</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F89" t="s">
         <v>95</v>
       </c>
-      <c r="E89" t="s">
+      <c r="G89" t="s">
         <v>96</v>
       </c>
-      <c r="F89">
-        <v>0</v>
-      </c>
-      <c r="G89">
-        <v>1</v>
-      </c>
       <c r="H89" t="s">
+        <v>267</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89" t="s">
         <v>116</v>
       </c>
-      <c r="I89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>60</v>
       </c>
@@ -4194,26 +4694,32 @@
       <c r="C90" t="s">
         <v>95</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F90" t="s">
         <v>97</v>
       </c>
-      <c r="E90" t="s">
+      <c r="G90" t="s">
         <v>80</v>
       </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-      <c r="G90">
-        <v>1</v>
-      </c>
       <c r="H90" t="s">
+        <v>267</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90" t="s">
         <v>90</v>
       </c>
-      <c r="I90">
+      <c r="K90">
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>60</v>
       </c>
@@ -4223,26 +4729,32 @@
       <c r="C91" t="s">
         <v>97</v>
       </c>
-      <c r="D91" t="s">
-        <v>82</v>
-      </c>
-      <c r="E91" t="s">
+      <c r="D91" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F91" t="s">
+        <v>82</v>
+      </c>
+      <c r="G91" t="s">
         <v>95</v>
       </c>
-      <c r="F91">
-        <v>0</v>
-      </c>
-      <c r="G91">
-        <v>2</v>
-      </c>
       <c r="H91" t="s">
+        <v>267</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
+      </c>
+      <c r="J91" t="s">
         <v>85</v>
       </c>
-      <c r="I91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>60</v>
       </c>
@@ -4252,23 +4764,29 @@
       <c r="C92" t="s">
         <v>82</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F92" t="s">
         <v>114</v>
       </c>
-      <c r="E92" t="s">
+      <c r="G92" t="s">
         <v>97</v>
       </c>
-      <c r="F92">
-        <v>2</v>
-      </c>
-      <c r="G92">
+      <c r="H92" t="s">
+        <v>34</v>
+      </c>
+      <c r="I92">
         <v>3</v>
       </c>
-      <c r="I92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>60</v>
       </c>
@@ -4278,26 +4796,32 @@
       <c r="C93" t="s">
         <v>114</v>
       </c>
-      <c r="D93" t="s">
-        <v>82</v>
-      </c>
-      <c r="E93" t="s">
-        <v>82</v>
-      </c>
-      <c r="F93">
-        <v>0</v>
-      </c>
-      <c r="G93">
-        <v>2</v>
+      <c r="D93" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F93" t="s">
+        <v>82</v>
+      </c>
+      <c r="G93" t="s">
+        <v>82</v>
       </c>
       <c r="H93" t="s">
+        <v>267</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+      <c r="J93" t="s">
         <v>92</v>
       </c>
-      <c r="I93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>60</v>
       </c>
@@ -4307,23 +4831,29 @@
       <c r="C94" t="s">
         <v>82</v>
       </c>
-      <c r="D94" t="s">
-        <v>82</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="D94" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F94" t="s">
+        <v>82</v>
+      </c>
+      <c r="G94" t="s">
         <v>114</v>
       </c>
-      <c r="F94">
-        <v>2</v>
-      </c>
-      <c r="G94">
-        <v>2</v>
+      <c r="H94" t="s">
+        <v>34</v>
       </c>
       <c r="I94">
         <v>2</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>60</v>
       </c>
@@ -4333,23 +4863,29 @@
       <c r="C95" t="s">
         <v>82</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F95" t="s">
         <v>107</v>
       </c>
-      <c r="E95" t="s">
-        <v>82</v>
-      </c>
-      <c r="F95">
-        <v>1</v>
-      </c>
-      <c r="G95">
-        <v>2</v>
+      <c r="G95" t="s">
+        <v>82</v>
+      </c>
+      <c r="H95" t="s">
+        <v>33</v>
       </c>
       <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="K95">
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>60</v>
       </c>
@@ -4359,23 +4895,26 @@
       <c r="C96" t="s">
         <v>107</v>
       </c>
-      <c r="E96" t="s">
-        <v>82</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
-      <c r="G96">
-        <v>1</v>
+      <c r="E96" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G96" t="s">
+        <v>82</v>
       </c>
       <c r="H96" t="s">
+        <v>267</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96" t="s">
         <v>103</v>
       </c>
-      <c r="I96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>61</v>
       </c>
@@ -4385,20 +4924,23 @@
       <c r="C97" t="s">
         <v>78</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F97" t="s">
         <v>104</v>
       </c>
-      <c r="F97">
-        <v>0</v>
-      </c>
-      <c r="G97">
-        <v>0</v>
+      <c r="H97" t="s">
+        <v>267</v>
       </c>
       <c r="I97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>61</v>
       </c>
@@ -4408,26 +4950,32 @@
       <c r="C98" t="s">
         <v>104</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F98" t="s">
         <v>105</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>78</v>
       </c>
-      <c r="F98">
-        <v>0</v>
-      </c>
-      <c r="G98">
-        <v>1</v>
-      </c>
       <c r="H98" t="s">
+        <v>267</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98" t="s">
         <v>108</v>
       </c>
-      <c r="I98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>61</v>
       </c>
@@ -4437,26 +4985,32 @@
       <c r="C99" t="s">
         <v>105</v>
       </c>
-      <c r="D99" t="s">
-        <v>82</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="D99" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F99" t="s">
+        <v>82</v>
+      </c>
+      <c r="G99" t="s">
         <v>104</v>
       </c>
-      <c r="F99">
-        <v>0</v>
-      </c>
-      <c r="G99">
-        <v>1</v>
-      </c>
       <c r="H99" t="s">
+        <v>267</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99" t="s">
         <v>117</v>
       </c>
-      <c r="I99">
+      <c r="K99">
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>61</v>
       </c>
@@ -4466,23 +5020,29 @@
       <c r="C100" t="s">
         <v>82</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F100" t="s">
         <v>80</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>105</v>
       </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-      <c r="G100">
-        <v>1</v>
+      <c r="H100" t="s">
+        <v>33</v>
       </c>
       <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="K100">
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>61</v>
       </c>
@@ -4492,23 +5052,29 @@
       <c r="C101" t="s">
         <v>80</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F101" t="s">
         <v>106</v>
       </c>
-      <c r="E101" t="s">
-        <v>82</v>
-      </c>
-      <c r="F101">
-        <v>1</v>
-      </c>
-      <c r="G101">
-        <v>1</v>
+      <c r="G101" t="s">
+        <v>82</v>
+      </c>
+      <c r="H101" t="s">
+        <v>33</v>
       </c>
       <c r="I101">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>61</v>
       </c>
@@ -4518,26 +5084,32 @@
       <c r="C102" t="s">
         <v>106</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F102" t="s">
         <v>97</v>
       </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>80</v>
       </c>
-      <c r="F102">
-        <v>0</v>
-      </c>
-      <c r="G102">
-        <v>1</v>
-      </c>
       <c r="H102" t="s">
+        <v>267</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102" t="s">
         <v>111</v>
       </c>
-      <c r="I102">
+      <c r="K102">
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>61</v>
       </c>
@@ -4547,26 +5119,32 @@
       <c r="C103" t="s">
         <v>97</v>
       </c>
-      <c r="D103" t="s">
-        <v>82</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="D103" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F103" t="s">
+        <v>82</v>
+      </c>
+      <c r="G103" t="s">
         <v>106</v>
       </c>
-      <c r="F103">
-        <v>0</v>
-      </c>
-      <c r="G103">
+      <c r="H103" t="s">
+        <v>267</v>
+      </c>
+      <c r="I103">
         <v>3</v>
       </c>
-      <c r="H103" t="s">
+      <c r="J103" t="s">
         <v>85</v>
       </c>
-      <c r="I103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>61</v>
       </c>
@@ -4576,23 +5154,29 @@
       <c r="C104" t="s">
         <v>82</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F104" t="s">
         <v>114</v>
       </c>
-      <c r="E104" t="s">
+      <c r="G104" t="s">
         <v>97</v>
       </c>
-      <c r="F104">
-        <v>2</v>
-      </c>
-      <c r="G104">
+      <c r="H104" t="s">
+        <v>34</v>
+      </c>
+      <c r="I104">
         <v>3</v>
       </c>
-      <c r="I104">
+      <c r="K104">
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>61</v>
       </c>
@@ -4602,26 +5186,32 @@
       <c r="C105" t="s">
         <v>114</v>
       </c>
-      <c r="D105" t="s">
-        <v>82</v>
-      </c>
-      <c r="E105" t="s">
-        <v>82</v>
-      </c>
-      <c r="F105">
-        <v>0</v>
-      </c>
-      <c r="G105">
-        <v>2</v>
+      <c r="D105" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F105" t="s">
+        <v>82</v>
+      </c>
+      <c r="G105" t="s">
+        <v>82</v>
       </c>
       <c r="H105" t="s">
+        <v>267</v>
+      </c>
+      <c r="I105">
+        <v>2</v>
+      </c>
+      <c r="J105" t="s">
         <v>92</v>
       </c>
-      <c r="I105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>61</v>
       </c>
@@ -4631,23 +5221,29 @@
       <c r="C106" t="s">
         <v>82</v>
       </c>
-      <c r="D106" t="s">
-        <v>82</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="D106" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F106" t="s">
+        <v>82</v>
+      </c>
+      <c r="G106" t="s">
         <v>114</v>
       </c>
-      <c r="F106">
-        <v>2</v>
-      </c>
-      <c r="G106">
-        <v>2</v>
+      <c r="H106" t="s">
+        <v>34</v>
       </c>
       <c r="I106">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>61</v>
       </c>
@@ -4657,23 +5253,29 @@
       <c r="C107" t="s">
         <v>82</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F107" t="s">
         <v>107</v>
       </c>
-      <c r="E107" t="s">
-        <v>82</v>
-      </c>
-      <c r="F107">
-        <v>1</v>
-      </c>
-      <c r="G107">
-        <v>2</v>
+      <c r="G107" t="s">
+        <v>82</v>
+      </c>
+      <c r="H107" t="s">
+        <v>33</v>
       </c>
       <c r="I107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>61</v>
       </c>
@@ -4683,23 +5285,26 @@
       <c r="C108" t="s">
         <v>107</v>
       </c>
-      <c r="E108" t="s">
-        <v>82</v>
-      </c>
-      <c r="F108">
-        <v>0</v>
-      </c>
-      <c r="G108">
-        <v>2</v>
+      <c r="E108" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G108" t="s">
+        <v>82</v>
       </c>
       <c r="H108" t="s">
+        <v>267</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="J108" t="s">
         <v>113</v>
       </c>
-      <c r="I108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>62</v>
       </c>
@@ -4709,20 +5314,23 @@
       <c r="C109" t="s">
         <v>78</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F109" t="s">
         <v>96</v>
       </c>
-      <c r="F109">
-        <v>0</v>
-      </c>
-      <c r="G109">
-        <v>0</v>
+      <c r="H109" t="s">
+        <v>267</v>
       </c>
       <c r="I109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>62</v>
       </c>
@@ -4732,26 +5340,32 @@
       <c r="C110" t="s">
         <v>96</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F110" t="s">
         <v>80</v>
       </c>
-      <c r="E110" t="s">
+      <c r="G110" t="s">
         <v>78</v>
       </c>
-      <c r="F110">
-        <v>0</v>
-      </c>
-      <c r="G110">
-        <v>1</v>
-      </c>
       <c r="H110" t="s">
+        <v>267</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110" t="s">
         <v>101</v>
       </c>
-      <c r="I110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>62</v>
       </c>
@@ -4761,26 +5375,32 @@
       <c r="C111" t="s">
         <v>80</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F111" t="s">
         <v>95</v>
       </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>96</v>
       </c>
-      <c r="F111">
-        <v>0</v>
-      </c>
-      <c r="G111">
-        <v>1</v>
-      </c>
       <c r="H111" t="s">
+        <v>267</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111" t="s">
         <v>116</v>
       </c>
-      <c r="I111">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>62</v>
       </c>
@@ -4790,26 +5410,32 @@
       <c r="C112" t="s">
         <v>95</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F112" t="s">
         <v>97</v>
       </c>
-      <c r="E112" t="s">
+      <c r="G112" t="s">
         <v>80</v>
       </c>
-      <c r="F112">
-        <v>0</v>
-      </c>
-      <c r="G112">
-        <v>1</v>
-      </c>
       <c r="H112" t="s">
+        <v>267</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112" t="s">
         <v>90</v>
       </c>
-      <c r="I112">
+      <c r="K112">
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>62</v>
       </c>
@@ -4819,26 +5445,32 @@
       <c r="C113" t="s">
         <v>97</v>
       </c>
-      <c r="D113" t="s">
-        <v>82</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="D113" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F113" t="s">
+        <v>82</v>
+      </c>
+      <c r="G113" t="s">
         <v>95</v>
       </c>
-      <c r="F113">
-        <v>0</v>
-      </c>
-      <c r="G113">
-        <v>2</v>
-      </c>
       <c r="H113" t="s">
+        <v>267</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113" t="s">
         <v>85</v>
       </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>62</v>
       </c>
@@ -4848,23 +5480,29 @@
       <c r="C114" t="s">
         <v>82</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F114" t="s">
         <v>98</v>
       </c>
-      <c r="E114" t="s">
+      <c r="G114" t="s">
         <v>97</v>
       </c>
-      <c r="F114">
-        <v>2</v>
-      </c>
-      <c r="G114">
-        <v>2</v>
+      <c r="H114" t="s">
+        <v>34</v>
       </c>
       <c r="I114">
+        <v>2</v>
+      </c>
+      <c r="K114">
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>62</v>
       </c>
@@ -4874,26 +5512,32 @@
       <c r="C115" t="s">
         <v>98</v>
       </c>
-      <c r="D115" t="s">
-        <v>82</v>
-      </c>
-      <c r="E115" t="s">
-        <v>82</v>
-      </c>
-      <c r="F115">
-        <v>0</v>
-      </c>
-      <c r="G115">
-        <v>2</v>
+      <c r="D115" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F115" t="s">
+        <v>82</v>
+      </c>
+      <c r="G115" t="s">
+        <v>82</v>
       </c>
       <c r="H115" t="s">
+        <v>267</v>
+      </c>
+      <c r="I115">
+        <v>2</v>
+      </c>
+      <c r="J115" t="s">
         <v>92</v>
       </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>62</v>
       </c>
@@ -4903,23 +5547,29 @@
       <c r="C116" t="s">
         <v>82</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F116" t="s">
         <v>100</v>
       </c>
-      <c r="E116" t="s">
+      <c r="G116" t="s">
         <v>98</v>
       </c>
-      <c r="F116">
-        <v>1</v>
-      </c>
-      <c r="G116">
-        <v>1</v>
+      <c r="H116" t="s">
+        <v>33</v>
       </c>
       <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="K116">
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>62</v>
       </c>
@@ -4929,23 +5579,26 @@
       <c r="C117" t="s">
         <v>100</v>
       </c>
-      <c r="E117" t="s">
-        <v>82</v>
-      </c>
-      <c r="F117">
-        <v>0</v>
-      </c>
-      <c r="G117">
-        <v>1</v>
+      <c r="E117" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G117" t="s">
+        <v>82</v>
       </c>
       <c r="H117" t="s">
+        <v>267</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117" t="s">
         <v>103</v>
       </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>63</v>
       </c>
@@ -4955,20 +5608,23 @@
       <c r="C118" t="s">
         <v>78</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F118" t="s">
         <v>104</v>
       </c>
-      <c r="F118">
-        <v>0</v>
-      </c>
-      <c r="G118">
-        <v>0</v>
+      <c r="H118" t="s">
+        <v>267</v>
       </c>
       <c r="I118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>63</v>
       </c>
@@ -4978,26 +5634,32 @@
       <c r="C119" t="s">
         <v>104</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F119" t="s">
         <v>105</v>
       </c>
-      <c r="E119" t="s">
+      <c r="G119" t="s">
         <v>78</v>
       </c>
-      <c r="F119">
-        <v>0</v>
-      </c>
-      <c r="G119">
-        <v>1</v>
-      </c>
       <c r="H119" t="s">
+        <v>267</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119" t="s">
         <v>101</v>
       </c>
-      <c r="I119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>63</v>
       </c>
@@ -5007,26 +5669,32 @@
       <c r="C120" t="s">
         <v>105</v>
       </c>
-      <c r="D120" t="s">
-        <v>82</v>
-      </c>
-      <c r="E120" t="s">
+      <c r="D120" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F120" t="s">
+        <v>82</v>
+      </c>
+      <c r="G120" t="s">
         <v>104</v>
       </c>
-      <c r="F120">
-        <v>0</v>
-      </c>
-      <c r="G120">
-        <v>1</v>
-      </c>
       <c r="H120" t="s">
+        <v>267</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120" t="s">
         <v>109</v>
       </c>
-      <c r="I120">
+      <c r="K120">
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>63</v>
       </c>
@@ -5036,23 +5704,29 @@
       <c r="C121" t="s">
         <v>82</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F121" t="s">
         <v>80</v>
       </c>
-      <c r="E121" t="s">
+      <c r="G121" t="s">
         <v>105</v>
       </c>
-      <c r="F121">
-        <v>1</v>
-      </c>
-      <c r="G121">
-        <v>1</v>
+      <c r="H121" t="s">
+        <v>33</v>
       </c>
       <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="K121">
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>63</v>
       </c>
@@ -5062,23 +5736,29 @@
       <c r="C122" t="s">
         <v>80</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F122" t="s">
         <v>106</v>
       </c>
-      <c r="E122" t="s">
-        <v>82</v>
-      </c>
-      <c r="F122">
-        <v>1</v>
-      </c>
-      <c r="G122">
-        <v>1</v>
+      <c r="G122" t="s">
+        <v>82</v>
+      </c>
+      <c r="H122" t="s">
+        <v>33</v>
       </c>
       <c r="I122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>63</v>
       </c>
@@ -5088,26 +5768,32 @@
       <c r="C123" t="s">
         <v>106</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F123" t="s">
         <v>97</v>
       </c>
-      <c r="E123" t="s">
+      <c r="G123" t="s">
         <v>80</v>
       </c>
-      <c r="F123">
-        <v>0</v>
-      </c>
-      <c r="G123">
-        <v>1</v>
-      </c>
       <c r="H123" t="s">
+        <v>267</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123" t="s">
         <v>111</v>
       </c>
-      <c r="I123">
+      <c r="K123">
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>63</v>
       </c>
@@ -5117,26 +5803,32 @@
       <c r="C124" t="s">
         <v>97</v>
       </c>
-      <c r="D124" t="s">
-        <v>82</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="D124" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F124" t="s">
+        <v>82</v>
+      </c>
+      <c r="G124" t="s">
         <v>106</v>
       </c>
-      <c r="F124">
-        <v>0</v>
-      </c>
-      <c r="G124">
+      <c r="H124" t="s">
+        <v>267</v>
+      </c>
+      <c r="I124">
         <v>3</v>
       </c>
-      <c r="H124" t="s">
+      <c r="J124" t="s">
         <v>85</v>
       </c>
-      <c r="I124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>63</v>
       </c>
@@ -5146,23 +5838,29 @@
       <c r="C125" t="s">
         <v>82</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F125" t="s">
         <v>86</v>
       </c>
-      <c r="E125" t="s">
+      <c r="G125" t="s">
         <v>97</v>
       </c>
-      <c r="F125">
-        <v>2</v>
-      </c>
-      <c r="G125">
+      <c r="H125" t="s">
+        <v>34</v>
+      </c>
+      <c r="I125">
         <v>3</v>
       </c>
-      <c r="I125">
+      <c r="K125">
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>63</v>
       </c>
@@ -5172,26 +5870,32 @@
       <c r="C126" t="s">
         <v>86</v>
       </c>
-      <c r="D126" t="s">
-        <v>82</v>
-      </c>
-      <c r="E126" t="s">
-        <v>82</v>
-      </c>
-      <c r="F126">
-        <v>0</v>
-      </c>
-      <c r="G126">
+      <c r="D126" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F126" t="s">
+        <v>82</v>
+      </c>
+      <c r="G126" t="s">
+        <v>82</v>
+      </c>
+      <c r="H126" t="s">
+        <v>267</v>
+      </c>
+      <c r="I126">
         <v>3</v>
       </c>
-      <c r="H126" t="s">
+      <c r="J126" t="s">
         <v>92</v>
       </c>
-      <c r="I126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>63</v>
       </c>
@@ -5201,23 +5905,29 @@
       <c r="C127" t="s">
         <v>82</v>
       </c>
-      <c r="D127" t="s">
-        <v>82</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="D127" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F127" t="s">
+        <v>82</v>
+      </c>
+      <c r="G127" t="s">
         <v>86</v>
       </c>
-      <c r="F127">
-        <v>2</v>
-      </c>
-      <c r="G127">
+      <c r="H127" t="s">
+        <v>34</v>
+      </c>
+      <c r="I127">
         <v>3</v>
       </c>
-      <c r="I127">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>63</v>
       </c>
@@ -5227,23 +5937,29 @@
       <c r="C128" t="s">
         <v>82</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F128" t="s">
         <v>107</v>
       </c>
-      <c r="E128" t="s">
-        <v>82</v>
-      </c>
-      <c r="F128">
-        <v>1</v>
-      </c>
-      <c r="G128">
-        <v>2</v>
+      <c r="G128" t="s">
+        <v>82</v>
+      </c>
+      <c r="H128" t="s">
+        <v>33</v>
       </c>
       <c r="I128">
+        <v>2</v>
+      </c>
+      <c r="K128">
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>63</v>
       </c>
@@ -5253,26 +5969,32 @@
       <c r="C129" t="s">
         <v>107</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F129" t="s">
         <v>88</v>
       </c>
-      <c r="E129" t="s">
-        <v>82</v>
-      </c>
-      <c r="F129">
-        <v>0</v>
-      </c>
-      <c r="G129">
-        <v>2</v>
+      <c r="G129" t="s">
+        <v>82</v>
       </c>
       <c r="H129" t="s">
+        <v>267</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="J129" t="s">
         <v>113</v>
       </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>63</v>
       </c>
@@ -5282,26 +6004,32 @@
       <c r="C130" t="s">
         <v>88</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F130" t="s">
         <v>100</v>
       </c>
-      <c r="E130" t="s">
+      <c r="G130" t="s">
         <v>107</v>
       </c>
-      <c r="F130">
-        <v>0</v>
-      </c>
-      <c r="G130">
-        <v>2</v>
-      </c>
       <c r="H130" t="s">
+        <v>267</v>
+      </c>
+      <c r="I130">
+        <v>2</v>
+      </c>
+      <c r="J130" t="s">
         <v>113</v>
       </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>63</v>
       </c>
@@ -5311,23 +6039,26 @@
       <c r="C131" t="s">
         <v>100</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G131" t="s">
         <v>88</v>
       </c>
-      <c r="F131">
-        <v>0</v>
-      </c>
-      <c r="G131">
-        <v>2</v>
-      </c>
       <c r="H131" t="s">
+        <v>267</v>
+      </c>
+      <c r="I131">
+        <v>2</v>
+      </c>
+      <c r="J131" t="s">
         <v>113</v>
       </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>64</v>
       </c>
@@ -5337,20 +6068,23 @@
       <c r="C132" t="s">
         <v>78</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F132" t="s">
         <v>104</v>
       </c>
-      <c r="F132">
-        <v>0</v>
-      </c>
-      <c r="G132">
-        <v>0</v>
+      <c r="H132" t="s">
+        <v>267</v>
       </c>
       <c r="I132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>64</v>
       </c>
@@ -5360,26 +6094,32 @@
       <c r="C133" t="s">
         <v>104</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F133" t="s">
         <v>105</v>
       </c>
-      <c r="E133" t="s">
+      <c r="G133" t="s">
         <v>78</v>
       </c>
-      <c r="F133">
-        <v>0</v>
-      </c>
-      <c r="G133">
-        <v>1</v>
-      </c>
       <c r="H133" t="s">
+        <v>267</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133" t="s">
         <v>108</v>
       </c>
-      <c r="I133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>64</v>
       </c>
@@ -5389,26 +6129,32 @@
       <c r="C134" t="s">
         <v>105</v>
       </c>
-      <c r="D134" t="s">
-        <v>82</v>
-      </c>
-      <c r="E134" t="s">
+      <c r="D134" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F134" t="s">
+        <v>82</v>
+      </c>
+      <c r="G134" t="s">
         <v>104</v>
       </c>
-      <c r="F134">
-        <v>0</v>
-      </c>
-      <c r="G134">
-        <v>1</v>
-      </c>
       <c r="H134" t="s">
+        <v>267</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134" t="s">
         <v>117</v>
       </c>
-      <c r="I134">
+      <c r="K134">
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>64</v>
       </c>
@@ -5418,23 +6164,29 @@
       <c r="C135" t="s">
         <v>82</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F135" t="s">
         <v>80</v>
       </c>
-      <c r="E135" t="s">
+      <c r="G135" t="s">
         <v>105</v>
       </c>
-      <c r="F135">
-        <v>1</v>
-      </c>
-      <c r="G135">
-        <v>1</v>
+      <c r="H135" t="s">
+        <v>33</v>
       </c>
       <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="K135">
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>64</v>
       </c>
@@ -5444,23 +6196,29 @@
       <c r="C136" t="s">
         <v>80</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F136" t="s">
         <v>106</v>
       </c>
-      <c r="E136" t="s">
-        <v>82</v>
-      </c>
-      <c r="F136">
-        <v>1</v>
-      </c>
-      <c r="G136">
-        <v>1</v>
+      <c r="G136" t="s">
+        <v>82</v>
+      </c>
+      <c r="H136" t="s">
+        <v>33</v>
       </c>
       <c r="I136">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>64</v>
       </c>
@@ -5470,26 +6228,32 @@
       <c r="C137" t="s">
         <v>106</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F137" t="s">
         <v>97</v>
       </c>
-      <c r="E137" t="s">
+      <c r="G137" t="s">
         <v>80</v>
       </c>
-      <c r="F137">
-        <v>0</v>
-      </c>
-      <c r="G137">
-        <v>1</v>
-      </c>
       <c r="H137" t="s">
+        <v>267</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137" t="s">
         <v>111</v>
       </c>
-      <c r="I137">
+      <c r="K137">
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>64</v>
       </c>
@@ -5499,26 +6263,32 @@
       <c r="C138" t="s">
         <v>97</v>
       </c>
-      <c r="D138" t="s">
-        <v>82</v>
-      </c>
-      <c r="E138" t="s">
+      <c r="D138" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F138" t="s">
+        <v>82</v>
+      </c>
+      <c r="G138" t="s">
         <v>106</v>
       </c>
-      <c r="F138">
-        <v>0</v>
-      </c>
-      <c r="G138">
+      <c r="H138" t="s">
+        <v>267</v>
+      </c>
+      <c r="I138">
         <v>3</v>
       </c>
-      <c r="H138" t="s">
+      <c r="J138" t="s">
         <v>85</v>
       </c>
-      <c r="I138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>64</v>
       </c>
@@ -5528,23 +6298,29 @@
       <c r="C139" t="s">
         <v>82</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F139" t="s">
         <v>114</v>
       </c>
-      <c r="E139" t="s">
+      <c r="G139" t="s">
         <v>97</v>
       </c>
-      <c r="F139">
-        <v>2</v>
-      </c>
-      <c r="G139">
+      <c r="H139" t="s">
+        <v>34</v>
+      </c>
+      <c r="I139">
         <v>3</v>
       </c>
-      <c r="I139">
+      <c r="K139">
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>64</v>
       </c>
@@ -5554,26 +6330,32 @@
       <c r="C140" t="s">
         <v>114</v>
       </c>
-      <c r="D140" t="s">
-        <v>82</v>
-      </c>
-      <c r="E140" t="s">
-        <v>82</v>
-      </c>
-      <c r="F140">
-        <v>0</v>
-      </c>
-      <c r="G140">
-        <v>2</v>
+      <c r="D140" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F140" t="s">
+        <v>82</v>
+      </c>
+      <c r="G140" t="s">
+        <v>82</v>
       </c>
       <c r="H140" t="s">
+        <v>267</v>
+      </c>
+      <c r="I140">
+        <v>2</v>
+      </c>
+      <c r="J140" t="s">
         <v>92</v>
       </c>
-      <c r="I140">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>64</v>
       </c>
@@ -5583,23 +6365,29 @@
       <c r="C141" t="s">
         <v>82</v>
       </c>
-      <c r="D141" t="s">
-        <v>82</v>
-      </c>
-      <c r="E141" t="s">
+      <c r="D141" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F141" t="s">
+        <v>82</v>
+      </c>
+      <c r="G141" t="s">
         <v>114</v>
       </c>
-      <c r="F141">
-        <v>2</v>
-      </c>
-      <c r="G141">
-        <v>2</v>
+      <c r="H141" t="s">
+        <v>34</v>
       </c>
       <c r="I141">
         <v>2</v>
       </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>64</v>
       </c>
@@ -5609,23 +6397,29 @@
       <c r="C142" t="s">
         <v>82</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F142" t="s">
         <v>107</v>
       </c>
-      <c r="E142" t="s">
-        <v>82</v>
-      </c>
-      <c r="F142">
-        <v>1</v>
-      </c>
-      <c r="G142">
-        <v>2</v>
+      <c r="G142" t="s">
+        <v>82</v>
+      </c>
+      <c r="H142" t="s">
+        <v>33</v>
       </c>
       <c r="I142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>64</v>
       </c>
@@ -5635,23 +6429,26 @@
       <c r="C143" t="s">
         <v>107</v>
       </c>
-      <c r="E143" t="s">
-        <v>82</v>
-      </c>
-      <c r="F143">
-        <v>0</v>
-      </c>
-      <c r="G143">
-        <v>2</v>
+      <c r="E143" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G143" t="s">
+        <v>82</v>
       </c>
       <c r="H143" t="s">
+        <v>267</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143" t="s">
         <v>113</v>
       </c>
-      <c r="I143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B144" s="2"/>
     </row>
   </sheetData>
@@ -7946,7 +8743,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12FB3095-0DE8-7946-9F31-F607C18FE7AD}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -7984,8 +8781,17 @@
         <v>35</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>267</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 

--- a/ontology/v2.01/cellfie_import.xlsx
+++ b/ontology/v2.01/cellfie_import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurasla/Documents/GitHub/bedreflyt/ontology/v2.01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4B1CE6-09FB-0C4D-B754-16E816B9F624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC4686B-BECA-A34A-8194-10526635B1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16060" yWindow="500" windowWidth="45800" windowHeight="25280" activeTab="1" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="271">
   <si>
     <t>DIAGNOSIS</t>
   </si>
@@ -854,6 +854,9 @@
   </si>
   <si>
     <t>PREVIOUS</t>
+  </si>
+  <si>
+    <t>StuaVenterom</t>
   </si>
 </sst>
 </file>
@@ -2768,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>101</v>
+        <v>270</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -3094,7 +3097,7 @@
         <v>2</v>
       </c>
       <c r="J41" t="s">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -3822,7 +3825,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>101</v>
+        <v>270</v>
       </c>
       <c r="K63">
         <v>1</v>
@@ -4183,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>101</v>
+        <v>270</v>
       </c>
       <c r="K74">
         <v>1</v>
@@ -4643,7 +4646,7 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>101</v>
+        <v>270</v>
       </c>
       <c r="K88">
         <v>1</v>
@@ -4969,7 +4972,7 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="K98">
         <v>1</v>
@@ -5004,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>117</v>
+        <v>270</v>
       </c>
       <c r="K99">
         <v>4</v>
@@ -5359,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>101</v>
+        <v>270</v>
       </c>
       <c r="K110">
         <v>1</v>
@@ -5653,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>101</v>
+        <v>270</v>
       </c>
       <c r="K119">
         <v>1</v>
@@ -6113,7 +6116,7 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="K133">
         <v>1</v>
@@ -6148,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>117</v>
+        <v>270</v>
       </c>
       <c r="K134">
         <v>4</v>

--- a/ontology/v2.01/cellfie_import.xlsx
+++ b/ontology/v2.01/cellfie_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurasla/Documents/GitHub/bedreflyt/ontology/v2.01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC4686B-BECA-A34A-8194-10526635B1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B7D594-BAF3-FF45-BF4E-8DAF86ACF632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16060" yWindow="500" windowWidth="45800" windowHeight="25280" activeTab="1" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
+    <workbookView xWindow="14120" yWindow="1580" windowWidth="33300" windowHeight="22360" activeTab="8" xr2:uid="{983204F9-122D-394F-950F-2D5A32EBE426}"/>
   </bookViews>
   <sheets>
     <sheet name="TreatmentJourneys" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="268">
   <si>
     <t>DIAGNOSIS</t>
   </si>
@@ -220,9 +220,6 @@
     <t>S06.5 Standard</t>
   </si>
   <si>
-    <t>D32.5 Standard</t>
-  </si>
-  <si>
     <t>I67.1 Standard</t>
   </si>
   <si>
@@ -430,9 +427,6 @@
     <t>S06.5_Standard_STEP_0</t>
   </si>
   <si>
-    <t>D32.5_Standard_STEP_0</t>
-  </si>
-  <si>
     <t>I67.1_Standard_STEP_0</t>
   </si>
   <si>
@@ -464,9 +458,6 @@
   </si>
   <si>
     <t>S06.5_Standard_STEP_8</t>
-  </si>
-  <si>
-    <t>D32.5_Standard_STEP_10</t>
   </si>
   <si>
     <t>I67.1_Standard_STEP_13</t>
@@ -1286,16 +1277,16 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1306,7 +1297,7 @@
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2">
         <v>60</v>
@@ -1318,16 +1309,16 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H2">
         <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1338,7 +1329,7 @@
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3">
         <v>60</v>
@@ -1350,16 +1341,16 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H3">
         <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1370,7 +1361,7 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4">
         <v>60</v>
@@ -1382,16 +1373,16 @@
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H4">
         <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1402,7 +1393,7 @@
         <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -1414,16 +1405,16 @@
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H5">
         <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1434,7 +1425,7 @@
         <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -1446,16 +1437,16 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H6">
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1463,10 +1454,10 @@
         <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7">
         <v>60</v>
@@ -1478,16 +1469,16 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H7">
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="J7" t="s">
-        <v>140</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1495,10 +1486,10 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8">
         <v>60</v>
@@ -1510,16 +1501,16 @@
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H8">
         <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1527,10 +1518,10 @@
         <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -1542,16 +1533,16 @@
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H9">
         <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1559,10 +1550,10 @@
         <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10">
         <v>60</v>
@@ -1574,16 +1565,16 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H10">
         <v>11</v>
       </c>
       <c r="I10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1591,10 +1582,10 @@
         <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11">
         <v>60</v>
@@ -1606,16 +1597,16 @@
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H11">
         <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1623,10 +1614,10 @@
         <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12">
         <v>60</v>
@@ -1638,16 +1629,16 @@
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H12">
         <v>13</v>
       </c>
       <c r="I12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1655,10 +1646,10 @@
         <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13">
         <v>60</v>
@@ -1670,16 +1661,16 @@
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H13">
         <v>11</v>
       </c>
       <c r="I13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J13" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1763,16 +1754,16 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C1" t="s">
         <v>38</v>
       </c>
       <c r="D1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F1" t="s">
         <v>6</v>
@@ -1784,10 +1775,10 @@
         <v>10</v>
       </c>
       <c r="I1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K1" t="s">
         <v>11</v>
@@ -1798,19 +1789,19 @@
         <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
       <c r="H2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1824,31 +1815,31 @@
         <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" t="s">
         <v>79</v>
       </c>
-      <c r="D3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" t="s">
-        <v>80</v>
-      </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1859,22 +1850,22 @@
         <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" t="s">
         <v>80</v>
       </c>
-      <c r="D4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" t="s">
-        <v>81</v>
-      </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
         <v>35</v>
@@ -1891,22 +1882,22 @@
         <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s">
         <v>35</v>
@@ -1915,7 +1906,7 @@
         <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -1926,22 +1917,22 @@
         <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" t="s">
         <v>82</v>
       </c>
-      <c r="D6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" t="s">
-        <v>83</v>
-      </c>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
         <v>35</v>
@@ -1958,31 +1949,31 @@
         <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" t="s">
         <v>83</v>
       </c>
-      <c r="D7" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F7" t="s">
-        <v>84</v>
-      </c>
       <c r="G7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1993,31 +1984,31 @@
         <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" t="s">
         <v>84</v>
       </c>
-      <c r="D8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F8" t="s">
-        <v>85</v>
-      </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I8">
         <v>4</v>
       </c>
       <c r="J8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K8">
         <v>4</v>
@@ -2028,22 +2019,22 @@
         <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
         <v>34</v>
@@ -2052,7 +2043,7 @@
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -2063,22 +2054,22 @@
         <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s">
         <v>35</v>
@@ -2095,31 +2086,31 @@
         <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I11">
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -2130,22 +2121,22 @@
         <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s">
         <v>35</v>
@@ -2162,31 +2153,31 @@
         <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I13">
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -2197,22 +2188,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s">
         <v>35</v>
@@ -2229,31 +2220,31 @@
         <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F15" t="s">
         <v>87</v>
       </c>
-      <c r="D15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" t="s">
-        <v>158</v>
-      </c>
-      <c r="F15" t="s">
-        <v>88</v>
-      </c>
       <c r="G15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I15">
         <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -2264,25 +2255,25 @@
         <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I16">
         <v>3</v>
       </c>
       <c r="J16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -2293,19 +2284,19 @@
         <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="s">
+        <v>157</v>
+      </c>
+      <c r="F17" t="s">
         <v>78</v>
       </c>
-      <c r="D17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F17" t="s">
-        <v>79</v>
-      </c>
       <c r="H17" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2319,31 +2310,31 @@
         <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" t="s">
         <v>79</v>
       </c>
-      <c r="D18" t="s">
-        <v>161</v>
-      </c>
-      <c r="E18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" t="s">
-        <v>80</v>
-      </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I18">
         <v>4</v>
       </c>
       <c r="J18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -2354,22 +2345,22 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F19" t="s">
         <v>80</v>
       </c>
-      <c r="D19" t="s">
-        <v>162</v>
-      </c>
-      <c r="E19" t="s">
-        <v>160</v>
-      </c>
-      <c r="F19" t="s">
-        <v>81</v>
-      </c>
       <c r="G19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
         <v>35</v>
@@ -2386,31 +2377,31 @@
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E20" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K20">
         <v>2</v>
@@ -2421,31 +2412,31 @@
         <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E21" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K21">
         <v>5</v>
@@ -2456,31 +2447,31 @@
         <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I22">
         <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -2491,22 +2482,22 @@
         <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s">
         <v>35</v>
@@ -2523,31 +2514,31 @@
         <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I24">
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2558,22 +2549,22 @@
         <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E25" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s">
         <v>35</v>
@@ -2590,31 +2581,31 @@
         <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I26">
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2625,25 +2616,25 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E27" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I27">
         <v>4</v>
@@ -2657,31 +2648,31 @@
         <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28" t="s">
         <v>87</v>
       </c>
-      <c r="D28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="s">
-        <v>169</v>
-      </c>
-      <c r="F28" t="s">
-        <v>88</v>
-      </c>
       <c r="G28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2692,25 +2683,25 @@
         <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I29">
         <v>3</v>
       </c>
       <c r="J29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2721,19 +2712,19 @@
         <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2747,31 +2738,31 @@
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s">
+        <v>264</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
         <v>267</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-      <c r="J31" t="s">
-        <v>270</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -2782,31 +2773,31 @@
         <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E32" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H32" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -2817,22 +2808,22 @@
         <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E33" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s">
         <v>33</v>
@@ -2849,31 +2840,31 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K34">
         <v>3</v>
@@ -2884,31 +2875,31 @@
         <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I35">
         <v>2</v>
       </c>
       <c r="J35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2919,22 +2910,22 @@
         <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H36" t="s">
         <v>34</v>
@@ -2951,31 +2942,31 @@
         <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" t="s">
         <v>98</v>
       </c>
-      <c r="D37" t="s">
-        <v>178</v>
-      </c>
-      <c r="E37" t="s">
-        <v>176</v>
-      </c>
-      <c r="F37" t="s">
-        <v>99</v>
-      </c>
       <c r="G37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I37">
         <v>2</v>
       </c>
       <c r="J37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -2986,22 +2977,22 @@
         <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" t="s">
+        <v>174</v>
+      </c>
+      <c r="F38" t="s">
         <v>99</v>
       </c>
-      <c r="D38" t="s">
-        <v>137</v>
-      </c>
-      <c r="E38" t="s">
-        <v>177</v>
-      </c>
-      <c r="F38" t="s">
-        <v>100</v>
-      </c>
       <c r="G38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H38" t="s">
         <v>33</v>
@@ -3018,25 +3009,25 @@
         <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E39" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H39" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I39">
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -3047,19 +3038,19 @@
         <v>56</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H40" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3073,31 +3064,31 @@
         <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C41" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" t="s">
         <v>104</v>
       </c>
-      <c r="D41" t="s">
-        <v>180</v>
-      </c>
-      <c r="E41" t="s">
-        <v>126</v>
-      </c>
-      <c r="F41" t="s">
-        <v>105</v>
-      </c>
       <c r="G41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s">
+        <v>264</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41" t="s">
         <v>267</v>
-      </c>
-      <c r="I41">
-        <v>2</v>
-      </c>
-      <c r="J41" t="s">
-        <v>270</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -3108,31 +3099,31 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H42" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I42">
         <v>2</v>
       </c>
       <c r="J42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K42">
         <v>4</v>
@@ -3143,22 +3134,22 @@
         <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E43" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H43" t="s">
         <v>33</v>
@@ -3167,7 +3158,7 @@
         <v>2</v>
       </c>
       <c r="J43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K43">
         <v>16</v>
@@ -3178,22 +3169,22 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D44" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E44" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F44" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s">
         <v>33</v>
@@ -3202,7 +3193,7 @@
         <v>2</v>
       </c>
       <c r="J44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -3213,31 +3204,31 @@
         <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D45" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E45" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I45">
         <v>2</v>
       </c>
       <c r="J45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K45">
         <v>3</v>
@@ -3248,31 +3239,31 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E46" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H46" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I46">
         <v>3</v>
       </c>
       <c r="J46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K46">
         <v>1</v>
@@ -3283,22 +3274,22 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E47" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H47" t="s">
         <v>34</v>
@@ -3307,7 +3298,7 @@
         <v>3</v>
       </c>
       <c r="J47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K47">
         <v>24</v>
@@ -3318,31 +3309,31 @@
         <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D48" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E48" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I48">
         <v>3</v>
       </c>
       <c r="J48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -3353,22 +3344,22 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D49" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E49" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s">
         <v>34</v>
@@ -3388,22 +3379,22 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D50" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E50" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s">
         <v>33</v>
@@ -3423,31 +3414,31 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D51" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E51" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I51">
         <v>3</v>
       </c>
       <c r="J51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -3458,25 +3449,25 @@
         <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E52" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H52" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I52">
         <v>3</v>
       </c>
       <c r="J52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -3487,19 +3478,19 @@
         <v>57</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F53" t="s">
         <v>78</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F53" t="s">
-        <v>79</v>
-      </c>
       <c r="H53" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3513,31 +3504,31 @@
         <v>57</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C54" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" t="s">
         <v>79</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F54" t="s">
-        <v>80</v>
-      </c>
       <c r="G54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H54" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I54">
         <v>2</v>
       </c>
       <c r="J54" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K54">
         <v>1</v>
@@ -3548,22 +3539,22 @@
         <v>57</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s">
         <v>34</v>
@@ -3580,22 +3571,22 @@
         <v>57</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s">
         <v>33</v>
@@ -3612,31 +3603,31 @@
         <v>57</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I57">
         <v>3</v>
       </c>
       <c r="J57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K57">
         <v>3</v>
@@ -3647,22 +3638,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s">
         <v>34</v>
@@ -3679,31 +3670,31 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I59">
         <v>3</v>
       </c>
       <c r="J59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K59">
         <v>1</v>
@@ -3714,22 +3705,22 @@
         <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F60" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H60" t="s">
         <v>34</v>
@@ -3746,25 +3737,25 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I61">
         <v>2</v>
       </c>
       <c r="J61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -3772,22 +3763,22 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H62" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3798,34 +3789,34 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s">
+        <v>264</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
         <v>267</v>
-      </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-      <c r="J63" t="s">
-        <v>270</v>
       </c>
       <c r="K63">
         <v>1</v>
@@ -3833,34 +3824,34 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C64" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F64" t="s">
+        <v>94</v>
+      </c>
+      <c r="G64" t="s">
+        <v>95</v>
+      </c>
+      <c r="H64" t="s">
+        <v>264</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
         <v>115</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C64" t="s">
-        <v>80</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F64" t="s">
-        <v>95</v>
-      </c>
-      <c r="G64" t="s">
-        <v>96</v>
-      </c>
-      <c r="H64" t="s">
-        <v>267</v>
-      </c>
-      <c r="I64">
-        <v>1</v>
-      </c>
-      <c r="J64" t="s">
-        <v>116</v>
       </c>
       <c r="K64">
         <v>1</v>
@@ -3868,34 +3859,34 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I65">
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K65">
         <v>4</v>
@@ -3903,34 +3894,34 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I66">
         <v>2</v>
       </c>
       <c r="J66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K66">
         <v>1</v>
@@ -3938,25 +3929,25 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F67" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H67" t="s">
         <v>34</v>
@@ -3970,34 +3961,34 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C68" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I68">
         <v>2</v>
       </c>
       <c r="J68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K68">
         <v>1</v>
@@ -4005,25 +3996,25 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H69" t="s">
         <v>34</v>
@@ -4037,25 +4028,25 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F70" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s">
         <v>33</v>
@@ -4069,34 +4060,34 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I71">
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -4104,28 +4095,28 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C72" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H72" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I72">
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -4133,22 +4124,22 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H73" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -4159,34 +4150,34 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C74" t="s">
+        <v>103</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F74" t="s">
         <v>104</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F74" t="s">
-        <v>105</v>
-      </c>
       <c r="G74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H74" t="s">
+        <v>264</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74" t="s">
         <v>267</v>
-      </c>
-      <c r="I74">
-        <v>1</v>
-      </c>
-      <c r="J74" t="s">
-        <v>270</v>
       </c>
       <c r="K74">
         <v>1</v>
@@ -4194,34 +4185,34 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G75" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H75" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I75">
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K75">
         <v>4</v>
@@ -4229,25 +4220,25 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H76" t="s">
         <v>33</v>
@@ -4261,25 +4252,25 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F77" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s">
         <v>33</v>
@@ -4293,34 +4284,34 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I78">
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K78">
         <v>5</v>
@@ -4328,34 +4319,34 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C79" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G79" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H79" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I79">
         <v>3</v>
       </c>
       <c r="J79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K79">
         <v>1</v>
@@ -4363,25 +4354,25 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G80" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H80" t="s">
         <v>34</v>
@@ -4395,34 +4386,34 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I81">
         <v>3</v>
       </c>
       <c r="J81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K81">
         <v>1</v>
@@ -4430,25 +4421,25 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H82" t="s">
         <v>34</v>
@@ -4462,25 +4453,25 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s">
         <v>33</v>
@@ -4494,34 +4485,34 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I84">
         <v>2</v>
       </c>
       <c r="J84" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K84">
         <v>0</v>
@@ -4529,34 +4520,34 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C85" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F85" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G85" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H85" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I85">
         <v>2</v>
       </c>
       <c r="J85" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K85">
         <v>0</v>
@@ -4564,28 +4555,28 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C86" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G86" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H86" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I86">
         <v>2</v>
       </c>
       <c r="J86" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K86">
         <v>0</v>
@@ -4593,22 +4584,22 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F87" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H87" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4619,34 +4610,34 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H88" t="s">
+        <v>264</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88" t="s">
         <v>267</v>
-      </c>
-      <c r="I88">
-        <v>1</v>
-      </c>
-      <c r="J88" t="s">
-        <v>270</v>
       </c>
       <c r="K88">
         <v>1</v>
@@ -4654,34 +4645,34 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C89" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F89" t="s">
+        <v>94</v>
+      </c>
+      <c r="G89" t="s">
         <v>95</v>
       </c>
-      <c r="G89" t="s">
-        <v>96</v>
-      </c>
       <c r="H89" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I89">
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K89">
         <v>1</v>
@@ -4689,34 +4680,34 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H90" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I90">
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K90">
         <v>5</v>
@@ -4724,34 +4715,34 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F91" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H91" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I91">
         <v>2</v>
       </c>
       <c r="J91" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K91">
         <v>1</v>
@@ -4759,25 +4750,25 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C92" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F92" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H92" t="s">
         <v>34</v>
@@ -4791,34 +4782,34 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C93" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F93" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G93" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I93">
         <v>2</v>
       </c>
       <c r="J93" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K93">
         <v>1</v>
@@ -4826,25 +4817,25 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C94" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F94" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G94" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H94" t="s">
         <v>34</v>
@@ -4858,25 +4849,25 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C95" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G95" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s">
         <v>33</v>
@@ -4890,28 +4881,28 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C96" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G96" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I96">
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K96">
         <v>0</v>
@@ -4919,22 +4910,22 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H97" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4945,34 +4936,34 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C98" t="s">
+        <v>103</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F98" t="s">
         <v>104</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F98" t="s">
-        <v>105</v>
-      </c>
       <c r="G98" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H98" t="s">
+        <v>264</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98" t="s">
         <v>267</v>
-      </c>
-      <c r="I98">
-        <v>1</v>
-      </c>
-      <c r="J98" t="s">
-        <v>270</v>
       </c>
       <c r="K98">
         <v>1</v>
@@ -4980,34 +4971,34 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C99" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H99" t="s">
+        <v>264</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99" t="s">
         <v>267</v>
-      </c>
-      <c r="I99">
-        <v>1</v>
-      </c>
-      <c r="J99" t="s">
-        <v>270</v>
       </c>
       <c r="K99">
         <v>4</v>
@@ -5015,25 +5006,25 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C100" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F100" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G100" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H100" t="s">
         <v>33</v>
@@ -5047,25 +5038,25 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F101" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G101" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s">
         <v>33</v>
@@ -5079,34 +5070,34 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F102" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G102" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H102" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I102">
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K102">
         <v>6</v>
@@ -5114,34 +5105,34 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C103" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F103" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H103" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I103">
         <v>3</v>
       </c>
       <c r="J103" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K103">
         <v>1</v>
@@ -5149,25 +5140,25 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C104" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F104" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G104" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H104" t="s">
         <v>34</v>
@@ -5181,34 +5172,34 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C105" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F105" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G105" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I105">
         <v>2</v>
       </c>
       <c r="J105" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K105">
         <v>1</v>
@@ -5216,25 +5207,25 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C106" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F106" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G106" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H106" t="s">
         <v>34</v>
@@ -5248,25 +5239,25 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C107" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F107" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G107" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s">
         <v>33</v>
@@ -5280,28 +5271,28 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C108" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G108" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I108">
         <v>2</v>
       </c>
       <c r="J108" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K108">
         <v>0</v>
@@ -5309,22 +5300,22 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C109" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F109" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H109" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -5335,34 +5326,34 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C110" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G110" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H110" t="s">
+        <v>264</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110" t="s">
         <v>267</v>
-      </c>
-      <c r="I110">
-        <v>1</v>
-      </c>
-      <c r="J110" t="s">
-        <v>270</v>
       </c>
       <c r="K110">
         <v>1</v>
@@ -5370,34 +5361,34 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C111" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F111" t="s">
+        <v>94</v>
+      </c>
+      <c r="G111" t="s">
         <v>95</v>
       </c>
-      <c r="G111" t="s">
-        <v>96</v>
-      </c>
       <c r="H111" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I111">
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K111">
         <v>1</v>
@@ -5405,34 +5396,34 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C112" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F112" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G112" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H112" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I112">
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K112">
         <v>3</v>
@@ -5440,34 +5431,34 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C113" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F113" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H113" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I113">
         <v>2</v>
       </c>
       <c r="J113" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K113">
         <v>0</v>
@@ -5475,25 +5466,25 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C114" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F114" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G114" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H114" t="s">
         <v>34</v>
@@ -5507,34 +5498,34 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C115" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F115" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G115" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I115">
         <v>2</v>
       </c>
       <c r="J115" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K115">
         <v>0</v>
@@ -5542,25 +5533,25 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C116" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F116" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G116" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H116" t="s">
         <v>33</v>
@@ -5574,28 +5565,28 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C117" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G117" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H117" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I117">
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K117">
         <v>0</v>
@@ -5603,22 +5594,22 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C118" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F118" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H118" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -5629,34 +5620,34 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C119" t="s">
+        <v>103</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F119" t="s">
         <v>104</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F119" t="s">
-        <v>105</v>
-      </c>
       <c r="G119" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H119" t="s">
+        <v>264</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119" t="s">
         <v>267</v>
-      </c>
-      <c r="I119">
-        <v>1</v>
-      </c>
-      <c r="J119" t="s">
-        <v>270</v>
       </c>
       <c r="K119">
         <v>1</v>
@@ -5664,34 +5655,34 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C120" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F120" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G120" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H120" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I120">
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K120">
         <v>4</v>
@@ -5699,25 +5690,25 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C121" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F121" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G121" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H121" t="s">
         <v>33</v>
@@ -5731,25 +5722,25 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C122" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F122" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G122" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s">
         <v>33</v>
@@ -5763,34 +5754,34 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C123" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F123" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G123" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H123" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I123">
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K123">
         <v>3</v>
@@ -5798,34 +5789,34 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C124" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F124" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G124" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H124" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I124">
         <v>3</v>
       </c>
       <c r="J124" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K124">
         <v>1</v>
@@ -5833,25 +5824,25 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C125" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F125" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G125" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H125" t="s">
         <v>34</v>
@@ -5865,34 +5856,34 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C126" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F126" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G126" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H126" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I126">
         <v>3</v>
       </c>
       <c r="J126" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K126">
         <v>1</v>
@@ -5900,25 +5891,25 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C127" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F127" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G127" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H127" t="s">
         <v>34</v>
@@ -5932,25 +5923,25 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C128" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F128" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G128" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s">
         <v>33</v>
@@ -5964,34 +5955,34 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C129" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F129" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G129" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I129">
         <v>2</v>
       </c>
       <c r="J129" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -5999,34 +5990,34 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C130" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F130" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G130" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H130" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I130">
         <v>2</v>
       </c>
       <c r="J130" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K130">
         <v>0</v>
@@ -6034,28 +6025,28 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C131" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G131" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H131" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I131">
         <v>2</v>
       </c>
       <c r="J131" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -6063,22 +6054,22 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C132" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F132" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H132" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -6089,34 +6080,34 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C133" t="s">
+        <v>103</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F133" t="s">
         <v>104</v>
       </c>
-      <c r="D133" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F133" t="s">
-        <v>105</v>
-      </c>
       <c r="G133" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H133" t="s">
+        <v>264</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133" t="s">
         <v>267</v>
-      </c>
-      <c r="I133">
-        <v>1</v>
-      </c>
-      <c r="J133" t="s">
-        <v>270</v>
       </c>
       <c r="K133">
         <v>1</v>
@@ -6124,34 +6115,34 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C134" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F134" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G134" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H134" t="s">
+        <v>264</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134" t="s">
         <v>267</v>
-      </c>
-      <c r="I134">
-        <v>1</v>
-      </c>
-      <c r="J134" t="s">
-        <v>270</v>
       </c>
       <c r="K134">
         <v>4</v>
@@ -6159,25 +6150,25 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C135" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F135" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G135" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H135" t="s">
         <v>33</v>
@@ -6191,25 +6182,25 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C136" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F136" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G136" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s">
         <v>33</v>
@@ -6223,34 +6214,34 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C137" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F137" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G137" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H137" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I137">
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K137">
         <v>6</v>
@@ -6258,34 +6249,34 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C138" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F138" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G138" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H138" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I138">
         <v>3</v>
       </c>
       <c r="J138" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K138">
         <v>1</v>
@@ -6293,25 +6284,25 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C139" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F139" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G139" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H139" t="s">
         <v>34</v>
@@ -6325,34 +6316,34 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C140" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F140" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G140" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H140" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I140">
         <v>2</v>
       </c>
       <c r="J140" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K140">
         <v>1</v>
@@ -6360,25 +6351,25 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C141" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F141" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G141" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H141" t="s">
         <v>34</v>
@@ -6392,25 +6383,25 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C142" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F142" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G142" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H142" t="s">
         <v>33</v>
@@ -6424,28 +6415,28 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C143" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G143" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I143">
         <v>2</v>
       </c>
       <c r="J143" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -6481,10 +6472,10 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E1" t="s">
         <v>11</v>
@@ -6492,7 +6483,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6501,7 +6492,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -6509,7 +6500,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6523,7 +6514,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6537,7 +6528,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6551,7 +6542,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6565,7 +6556,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6579,7 +6570,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6593,7 +6584,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6607,7 +6598,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -6621,7 +6612,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6635,7 +6626,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6649,7 +6640,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6663,7 +6654,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6677,7 +6668,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6686,7 +6677,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -6694,7 +6685,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6703,7 +6694,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -6711,7 +6702,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6720,7 +6711,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -6728,7 +6719,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6737,7 +6728,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6745,7 +6736,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -6754,7 +6745,7 @@
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -6762,7 +6753,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6771,7 +6762,7 @@
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -6779,7 +6770,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6788,7 +6779,7 @@
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -6796,7 +6787,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6805,7 +6796,7 @@
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -6813,7 +6804,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6822,7 +6813,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -6830,7 +6821,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6839,7 +6830,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -6847,7 +6838,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6856,7 +6847,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -6864,7 +6855,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -6873,7 +6864,7 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -6881,7 +6872,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27">
         <v>3</v>
@@ -6890,7 +6881,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -6898,7 +6889,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -6907,7 +6898,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -6915,7 +6906,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -6929,7 +6920,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B30">
         <v>3</v>
@@ -6943,7 +6934,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -6952,7 +6943,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -6960,7 +6951,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -6974,7 +6965,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -6983,7 +6974,7 @@
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -6991,7 +6982,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -7005,7 +6996,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -7019,7 +7010,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -7028,7 +7019,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -7036,7 +7027,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -7050,7 +7041,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -7059,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -7067,7 +7058,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -7081,7 +7072,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -7090,7 +7081,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -7098,7 +7089,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -7112,7 +7103,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -7126,7 +7117,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -7135,7 +7126,7 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -7143,7 +7134,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -7152,7 +7143,7 @@
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -7160,7 +7151,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -7169,7 +7160,7 @@
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -7177,7 +7168,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -7186,7 +7177,7 @@
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -7194,7 +7185,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B47">
         <v>3</v>
@@ -7208,7 +7199,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B48">
         <v>3</v>
@@ -7222,7 +7213,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B49">
         <v>3</v>
@@ -7236,7 +7227,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B50">
         <v>3</v>
@@ -7250,7 +7241,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B51">
         <v>3</v>
@@ -7264,7 +7255,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B52">
         <v>3</v>
@@ -7278,7 +7269,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -7292,7 +7283,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -7306,7 +7297,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -7315,7 +7306,7 @@
         <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E55">
         <v>16</v>
@@ -7323,7 +7314,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -7332,7 +7323,7 @@
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E56">
         <v>24</v>
@@ -7340,7 +7331,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -7357,7 +7348,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -7374,7 +7365,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -7388,7 +7379,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -7402,7 +7393,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -7416,7 +7407,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -7430,7 +7421,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -7444,7 +7435,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -7458,7 +7449,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -7472,7 +7463,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -7486,7 +7477,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -7500,7 +7491,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -7514,7 +7505,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -7528,7 +7519,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -7542,7 +7533,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -7556,7 +7547,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -7570,7 +7561,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -7584,7 +7575,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -7598,7 +7589,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -7612,7 +7603,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -7626,7 +7617,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -7640,7 +7631,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -7654,7 +7645,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -7668,7 +7659,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -7682,7 +7673,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -7696,7 +7687,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -7710,7 +7701,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -7724,7 +7715,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -7738,7 +7729,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -7747,7 +7738,7 @@
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E85">
         <v>5</v>
@@ -7755,7 +7746,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -7764,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E86">
         <v>3</v>
@@ -7772,7 +7763,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -7781,7 +7772,7 @@
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E87">
         <v>3</v>
@@ -7789,7 +7780,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -7798,7 +7789,7 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E88">
         <v>4</v>
@@ -7806,7 +7797,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -7815,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E89">
         <v>5</v>
@@ -7823,7 +7814,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -7832,7 +7823,7 @@
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E90">
         <v>3</v>
@@ -7840,7 +7831,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -7849,7 +7840,7 @@
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E91">
         <v>3</v>
@@ -7857,7 +7848,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -7866,7 +7857,7 @@
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E92">
         <v>5</v>
@@ -7874,7 +7865,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -7883,7 +7874,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E93">
         <v>6</v>
@@ -7891,7 +7882,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -7900,7 +7891,7 @@
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E94">
         <v>3</v>
@@ -7908,7 +7899,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -7917,7 +7908,7 @@
         <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E95">
         <v>6</v>
@@ -7925,7 +7916,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -7934,7 +7925,7 @@
         <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E96">
         <v>1</v>
@@ -7942,7 +7933,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -7951,7 +7942,7 @@
         <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -7959,7 +7950,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -7968,7 +7959,7 @@
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -7976,7 +7967,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -7985,7 +7976,7 @@
         <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -7993,7 +7984,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -8002,7 +7993,7 @@
         <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -8010,7 +8001,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -8019,7 +8010,7 @@
         <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -8027,7 +8018,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -8036,7 +8027,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -8044,7 +8035,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -8053,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -8061,7 +8052,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -8070,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E104">
         <v>1</v>
@@ -8078,7 +8069,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B105">
         <v>2</v>
@@ -8087,7 +8078,7 @@
         <v>4</v>
       </c>
       <c r="D105" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E105">
         <v>1</v>
@@ -8095,7 +8086,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -8104,7 +8095,7 @@
         <v>4</v>
       </c>
       <c r="D106" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E106">
         <v>1</v>
@@ -8112,7 +8103,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -8121,7 +8112,7 @@
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -8129,7 +8120,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -8138,7 +8129,7 @@
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E108">
         <v>1</v>
@@ -8146,7 +8137,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -8155,7 +8146,7 @@
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -8163,7 +8154,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -8172,7 +8163,7 @@
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -8180,7 +8171,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -8189,7 +8180,7 @@
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -8197,7 +8188,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -8206,7 +8197,7 @@
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -8214,7 +8205,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -8223,7 +8214,7 @@
         <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -8231,7 +8222,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -8240,7 +8231,7 @@
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E114">
         <v>1</v>
@@ -8248,7 +8239,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -8257,7 +8248,7 @@
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -8265,7 +8256,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -8274,7 +8265,7 @@
         <v>2</v>
       </c>
       <c r="D116" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E116">
         <v>4</v>
@@ -8282,7 +8273,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -8291,7 +8282,7 @@
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E117">
         <v>4</v>
@@ -8299,7 +8290,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -8308,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E118">
         <v>4</v>
@@ -8316,7 +8307,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -8325,7 +8316,7 @@
         <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E119">
         <v>4</v>
@@ -8333,7 +8324,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -8342,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="D120" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E120">
         <v>4</v>
@@ -8350,7 +8341,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -8359,7 +8350,7 @@
         <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -8367,7 +8358,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -8376,7 +8367,7 @@
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8384,7 +8375,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -8398,7 +8389,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -8407,7 +8398,7 @@
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -8415,7 +8406,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -8424,7 +8415,7 @@
         <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8432,7 +8423,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -8441,7 +8432,7 @@
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -8449,7 +8440,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -8458,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="D127" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8466,7 +8457,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -8475,7 +8466,7 @@
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -8483,7 +8474,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -8492,7 +8483,7 @@
         <v>3</v>
       </c>
       <c r="D129" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8500,7 +8491,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -8509,7 +8500,7 @@
         <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8517,7 +8508,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -8526,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="D131" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8534,7 +8525,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -8543,7 +8534,7 @@
         <v>2</v>
       </c>
       <c r="D132" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8551,7 +8542,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8560,7 +8551,7 @@
         <v>1</v>
       </c>
       <c r="D133" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8568,7 +8559,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -8577,7 +8568,7 @@
         <v>2</v>
       </c>
       <c r="D134" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8585,7 +8576,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8594,7 +8585,7 @@
         <v>2</v>
       </c>
       <c r="D135" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8602,7 +8593,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8611,7 +8602,7 @@
         <v>2</v>
       </c>
       <c r="D136" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8619,7 +8610,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8628,7 +8619,7 @@
         <v>3</v>
       </c>
       <c r="D137" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -8636,7 +8627,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8645,7 +8636,7 @@
         <v>3</v>
       </c>
       <c r="D138" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -8653,7 +8644,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8662,7 +8653,7 @@
         <v>3</v>
       </c>
       <c r="D139" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8670,7 +8661,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -8679,7 +8670,7 @@
         <v>2</v>
       </c>
       <c r="D140" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8687,7 +8678,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -8696,7 +8687,7 @@
         <v>2</v>
       </c>
       <c r="D141" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8704,7 +8695,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -8713,7 +8704,7 @@
         <v>4</v>
       </c>
       <c r="D142" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E142">
         <v>1</v>
@@ -8721,7 +8712,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -8730,7 +8721,7 @@
         <v>4</v>
       </c>
       <c r="D143" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E143">
         <v>1</v>
@@ -8789,7 +8780,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -8948,7 +8939,7 @@
   <cols>
     <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.1640625" customWidth="1"/>
@@ -8978,14 +8969,14 @@
       <c r="B2">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>3</v>
+      <c r="C2" t="s">
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="E2">
-        <v>2</v>
+      <c r="E2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -8995,14 +8986,14 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>3</v>
+      <c r="C3" t="s">
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>37</v>
       </c>
-      <c r="E3">
-        <v>3</v>
+      <c r="E3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -9012,14 +9003,14 @@
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>3</v>
+      <c r="C4" t="s">
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
       </c>
-      <c r="E4">
-        <v>1</v>
+      <c r="E4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -9029,14 +9020,14 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>3</v>
+      <c r="C5" t="s">
+        <v>24</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="E5">
-        <v>2</v>
+      <c r="E5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
